--- a/outputs/wenkb-test-book-in-progress/第14小组_基于大模型的个人知识库系统_测试成绩书.xlsx
+++ b/outputs/wenkb-test-book-in-progress/第14小组_基于大模型的个人知识库系统_测试成绩书.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文件封面" sheetId="1" r:id="R8be615ed5725474b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试项目" sheetId="2" r:id="R9d6e0ad9dc0e4f2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI界面" sheetId="3" r:id="Reaf8fc1e7f7b4ffe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="运行" sheetId="4" r:id="Rd75ea493da1a4dd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文件封面" sheetId="1" r:id="R4ad4a0728dd34645"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试项目" sheetId="2" r:id="R3d94d4b9f5554adc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI界面" sheetId="3" r:id="R5b5654dcb3fc4be3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="运行" sheetId="4" r:id="Rccbcec2a52a7457f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,7 +20,7 @@
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -98,8 +98,13 @@
       <x:color rgb="FF1F2937"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF64748B"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -126,8 +131,13 @@
         <x:fgColor rgb="FFDCE6F1"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="10">
     <x:border>
       <x:left/>
       <x:right/>
@@ -150,11 +160,91 @@
       </x:bottom>
       <x:diagonal/>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFA6A6A6"/>
+      </x:left>
+      <x:right/>
+      <x:top style="thin">
+        <x:color rgb="FFA6A6A6"/>
+      </x:top>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top style="thin">
+        <x:color rgb="FFA6A6A6"/>
+      </x:top>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right style="thin">
+        <x:color rgb="FFA6A6A6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFA6A6A6"/>
+      </x:top>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFA6A6A6"/>
+      </x:left>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right style="thin">
+        <x:color rgb="FFA6A6A6"/>
+      </x:right>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFA6A6A6"/>
+      </x:left>
+      <x:right/>
+      <x:top/>
+      <x:bottom style="thin">
+        <x:color rgb="FFA6A6A6"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom style="thin">
+        <x:color rgb="FFA6A6A6"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right style="thin">
+        <x:color rgb="FFA6A6A6"/>
+      </x:right>
+      <x:top/>
+      <x:bottom style="thin">
+        <x:color rgb="FFA6A6A6"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="54">
+  <x:cellXfs count="83">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -313,11 +403,98 @@
     <x:xf numFmtId="200" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="9">
+  <x:dxfs count="12">
     <x:dxf>
       <x:font>
         <x:b/>
@@ -414,6 +591,39 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF375623"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C6500"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -920,7 +1130,7 @@
     </x:row>
     <x:row r="24" ht="30" customHeight="1">
       <x:c r="A24" s="14" t="str">
-        <x:v>测试项目：核心测试用例；UI界面：页面与流程验收映射；运行：执行汇总、状态判定与缺陷记录。</x:v>
+        <x:v>测试项目：核心测试用例；UI界面：页面与流程验收映射；运行：执行汇总、缺陷记录和实际运行截图留白。</x:v>
       </x:c>
       <x:c r="B24" s="14"/>
       <x:c r="C24" s="14"/>
@@ -3005,7 +3215,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree0df99a3aac4bfb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e3968e754514196"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3281,7 +3491,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra77dc007a26d4627"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbee11af59bef44bc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3298,6 +3508,7 @@
     <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -3311,6 +3522,7 @@
       <x:c r="F1" s="2"/>
       <x:c r="G1" s="2"/>
       <x:c r="H1" s="2"/>
+      <x:c r="I1" s="2"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="2"/>
@@ -3321,6 +3533,7 @@
       <x:c r="F2" s="2"/>
       <x:c r="G2" s="2"/>
       <x:c r="H2" s="2"/>
+      <x:c r="I2" s="2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
@@ -3335,6 +3548,7 @@
       <x:c r="F3" s="2"/>
       <x:c r="G3" s="2"/>
       <x:c r="H3" s="2"/>
+      <x:c r="I3" s="2"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
@@ -3349,6 +3563,7 @@
       <x:c r="F4" s="2"/>
       <x:c r="G4" s="2"/>
       <x:c r="H4" s="2"/>
+      <x:c r="I4" s="2"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="str">
@@ -3363,6 +3578,7 @@
       <x:c r="F5" s="2"/>
       <x:c r="G5" s="2"/>
       <x:c r="H5" s="2"/>
+      <x:c r="I5" s="2"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="str">
@@ -3377,6 +3593,7 @@
       <x:c r="F6" s="2"/>
       <x:c r="G6" s="2"/>
       <x:c r="H6" s="2"/>
+      <x:c r="I6" s="2"/>
     </x:row>
     <x:row r="7" ht="38" customHeight="1">
       <x:c r="A7" s="11" t="str">
@@ -3391,6 +3608,7 @@
       <x:c r="F7" s="2"/>
       <x:c r="G7" s="2"/>
       <x:c r="H7" s="2"/>
+      <x:c r="I7" s="2"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="2"/>
@@ -3401,6 +3619,7 @@
       <x:c r="F8" s="2"/>
       <x:c r="G8" s="2"/>
       <x:c r="H8" s="2"/>
+      <x:c r="I8" s="2"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="28" t="str">
@@ -3415,6 +3634,7 @@
       <x:c r="F9" s="2"/>
       <x:c r="G9" s="2"/>
       <x:c r="H9" s="2"/>
+      <x:c r="I9" s="2"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="40" t="str">
@@ -3430,6 +3650,7 @@
       <x:c r="F10" s="2"/>
       <x:c r="G10" s="2"/>
       <x:c r="H10" s="2"/>
+      <x:c r="I10" s="2"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="40" t="str">
@@ -3445,6 +3666,7 @@
       <x:c r="F11" s="2"/>
       <x:c r="G11" s="2"/>
       <x:c r="H11" s="2"/>
+      <x:c r="I11" s="2"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="40" t="str">
@@ -3460,6 +3682,7 @@
       <x:c r="F12" s="2"/>
       <x:c r="G12" s="2"/>
       <x:c r="H12" s="2"/>
+      <x:c r="I12" s="2"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="40" t="str">
@@ -3475,6 +3698,7 @@
       <x:c r="F13" s="2"/>
       <x:c r="G13" s="2"/>
       <x:c r="H13" s="2"/>
+      <x:c r="I13" s="2"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="40" t="str">
@@ -3490,6 +3714,7 @@
       <x:c r="F14" s="2"/>
       <x:c r="G14" s="2"/>
       <x:c r="H14" s="2"/>
+      <x:c r="I14" s="2"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="40" t="str">
@@ -3505,6 +3730,7 @@
       <x:c r="F15" s="2"/>
       <x:c r="G15" s="2"/>
       <x:c r="H15" s="2"/>
+      <x:c r="I15" s="2"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="40" t="str">
@@ -3520,6 +3746,7 @@
       <x:c r="F16" s="2"/>
       <x:c r="G16" s="2"/>
       <x:c r="H16" s="2"/>
+      <x:c r="I16" s="2"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="40" t="str">
@@ -3535,6 +3762,7 @@
       <x:c r="F17" s="2"/>
       <x:c r="G17" s="2"/>
       <x:c r="H17" s="2"/>
+      <x:c r="I17" s="2"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="40" t="str">
@@ -3550,6 +3778,7 @@
       <x:c r="F18" s="2"/>
       <x:c r="G18" s="2"/>
       <x:c r="H18" s="2"/>
+      <x:c r="I18" s="2"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="48" t="str">
@@ -3565,6 +3794,7 @@
       <x:c r="F19" s="2"/>
       <x:c r="G19" s="2"/>
       <x:c r="H19" s="2"/>
+      <x:c r="I19" s="2"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="2"/>
@@ -3575,27 +3805,27 @@
       <x:c r="F20" s="2"/>
       <x:c r="G20" s="2"/>
       <x:c r="H20" s="2"/>
+      <x:c r="I20" s="2"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="25" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B21" s="25" t="str">
-        <x:v>每轮测试前填写执行版本、环境和数据基线。</x:v>
-      </x:c>
+        <x:v>执行要求</x:v>
+      </x:c>
+      <x:c r="B21" s="25"/>
       <x:c r="C21" s="25"/>
       <x:c r="D21" s="25"/>
       <x:c r="E21" s="25"/>
       <x:c r="F21" s="25"/>
       <x:c r="G21" s="25"/>
       <x:c r="H21" s="25"/>
+      <x:c r="I21" s="2"/>
     </x:row>
     <x:row r="22" ht="26" customHeight="1">
       <x:c r="A22" s="52" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B22" s="31" t="str">
-        <x:v>每条用例执行后填写实测结果、确定结果、日期、测试者和证据。</x:v>
+        <x:v>每轮测试前填写执行版本、环境和数据基线。</x:v>
       </x:c>
       <x:c r="C22" s="31"/>
       <x:c r="D22" s="31"/>
@@ -3603,13 +3833,14 @@
       <x:c r="F22" s="31"/>
       <x:c r="G22" s="31"/>
       <x:c r="H22" s="31"/>
+      <x:c r="I22" s="2"/>
     </x:row>
     <x:row r="23" ht="26" customHeight="1">
       <x:c r="A23" s="52" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B23" s="31" t="str">
-        <x:v>失败或阻塞用例必须关联缺陷编号、日志或截图，并在回归后补充结论。</x:v>
+        <x:v>每条用例执行后填写实测结果、确定结果、日期、测试者和证据。</x:v>
       </x:c>
       <x:c r="C23" s="31"/>
       <x:c r="D23" s="31"/>
@@ -3617,13 +3848,14 @@
       <x:c r="F23" s="31"/>
       <x:c r="G23" s="31"/>
       <x:c r="H23" s="31"/>
+      <x:c r="I23" s="2"/>
     </x:row>
     <x:row r="24" ht="26" customHeight="1">
       <x:c r="A24" s="52" t="str">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B24" s="31" t="str">
-        <x:v>删除与重建测试只使用可恢复测试数据，执行前后保留对象清单。</x:v>
+        <x:v>失败或阻塞用例必须关联缺陷编号、日志或截图，并在回归后补充结论。</x:v>
       </x:c>
       <x:c r="C24" s="31"/>
       <x:c r="D24" s="31"/>
@@ -3631,13 +3863,14 @@
       <x:c r="F24" s="31"/>
       <x:c r="G24" s="31"/>
       <x:c r="H24" s="31"/>
+      <x:c r="I24" s="2"/>
     </x:row>
     <x:row r="25" ht="26" customHeight="1">
       <x:c r="A25" s="52" t="str">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B25" s="31" t="str">
-        <x:v>交付门禁：核心用例全部通过，高优先级缺陷清零或获得明确延期批准。</x:v>
+        <x:v>删除与重建测试只使用可恢复测试数据，执行前后保留对象清单。</x:v>
       </x:c>
       <x:c r="C25" s="31"/>
       <x:c r="D25" s="31"/>
@@ -3645,16 +3878,22 @@
       <x:c r="F25" s="31"/>
       <x:c r="G25" s="31"/>
       <x:c r="H25" s="31"/>
+      <x:c r="I25" s="2"/>
     </x:row>
     <x:row r="26" ht="26" customHeight="1">
-      <x:c r="A26" s="52"/>
-      <x:c r="B26" s="31"/>
+      <x:c r="A26" s="52" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B26" s="31" t="str">
+        <x:v>交付门禁：核心用例全部通过，高优先级缺陷清零或获得明确延期批准。</x:v>
+      </x:c>
       <x:c r="C26" s="31"/>
       <x:c r="D26" s="31"/>
       <x:c r="E26" s="31"/>
       <x:c r="F26" s="31"/>
       <x:c r="G26" s="31"/>
       <x:c r="H26" s="31"/>
+      <x:c r="I26" s="2"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="2"/>
@@ -3665,6 +3904,7 @@
       <x:c r="F27" s="2"/>
       <x:c r="G27" s="2"/>
       <x:c r="H27" s="2"/>
+      <x:c r="I27" s="2"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="2"/>
@@ -3675,6 +3915,7 @@
       <x:c r="F28" s="2"/>
       <x:c r="G28" s="2"/>
       <x:c r="H28" s="2"/>
+      <x:c r="I28" s="2"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="28" t="str">
@@ -3699,6 +3940,7 @@
         <x:v>关闭日期</x:v>
       </x:c>
       <x:c r="H29" s="2"/>
+      <x:c r="I29" s="2"/>
     </x:row>
     <x:row r="30" ht="25" customHeight="1">
       <x:c r="A30" s="31" t="str"/>
@@ -3709,6 +3951,7 @@
       <x:c r="F30" s="31" t="str"/>
       <x:c r="G30" s="53"/>
       <x:c r="H30" s="2"/>
+      <x:c r="I30" s="2"/>
     </x:row>
     <x:row r="31" ht="25" customHeight="1">
       <x:c r="A31" s="31" t="str"/>
@@ -3719,6 +3962,7 @@
       <x:c r="F31" s="31" t="str"/>
       <x:c r="G31" s="53"/>
       <x:c r="H31" s="2"/>
+      <x:c r="I31" s="2"/>
     </x:row>
     <x:row r="32" ht="25" customHeight="1">
       <x:c r="A32" s="31" t="str"/>
@@ -3729,6 +3973,7 @@
       <x:c r="F32" s="31" t="str"/>
       <x:c r="G32" s="53"/>
       <x:c r="H32" s="2"/>
+      <x:c r="I32" s="2"/>
     </x:row>
     <x:row r="33" ht="25" customHeight="1">
       <x:c r="A33" s="31" t="str"/>
@@ -3739,6 +3984,7 @@
       <x:c r="F33" s="31" t="str"/>
       <x:c r="G33" s="53"/>
       <x:c r="H33" s="2"/>
+      <x:c r="I33" s="2"/>
     </x:row>
     <x:row r="34" ht="25" customHeight="1">
       <x:c r="A34" s="31" t="str"/>
@@ -3749,16 +3995,984 @@
       <x:c r="F34" s="31" t="str"/>
       <x:c r="G34" s="53"/>
       <x:c r="H34" s="2"/>
+      <x:c r="I34" s="2"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="2"/>
+      <x:c r="B35" s="2"/>
+      <x:c r="C35" s="2"/>
+      <x:c r="D35" s="2"/>
+      <x:c r="E35" s="2"/>
+      <x:c r="F35" s="2"/>
+      <x:c r="G35" s="2"/>
+      <x:c r="H35" s="2"/>
+      <x:c r="I35" s="2"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="25" t="str">
+        <x:v>项目实际运行情况（待人工执行）</x:v>
+      </x:c>
+      <x:c r="B36" s="25"/>
+      <x:c r="C36" s="25"/>
+      <x:c r="D36" s="25"/>
+      <x:c r="E36" s="25"/>
+      <x:c r="F36" s="25"/>
+      <x:c r="G36" s="25"/>
+      <x:c r="H36" s="25"/>
+      <x:c r="I36" s="25"/>
+    </x:row>
+    <x:row r="37" ht="34" customHeight="1">
+      <x:c r="A37" s="54" t="str">
+        <x:v>依据 docs/test_scorebook_manual_run.md 在隔离副本中手动运行并粘贴截图。本区仅记录运行冒烟证据，不替代 48 条用例执行，也不改变交付判定。</x:v>
+      </x:c>
+      <x:c r="B37" s="54"/>
+      <x:c r="C37" s="54"/>
+      <x:c r="D37" s="54"/>
+      <x:c r="E37" s="54"/>
+      <x:c r="F37" s="54"/>
+      <x:c r="G37" s="54"/>
+      <x:c r="H37" s="54"/>
+      <x:c r="I37" s="54"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="2"/>
+      <x:c r="B38" s="2"/>
+      <x:c r="C38" s="2"/>
+      <x:c r="D38" s="2"/>
+      <x:c r="E38" s="2"/>
+      <x:c r="F38" s="2"/>
+      <x:c r="G38" s="2"/>
+      <x:c r="H38" s="2"/>
+      <x:c r="I38" s="2"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="56" t="str">
+        <x:v>运行环境记录</x:v>
+      </x:c>
+      <x:c r="B39" s="56"/>
+      <x:c r="C39" s="56"/>
+      <x:c r="D39" s="56"/>
+      <x:c r="E39" s="56"/>
+      <x:c r="F39" s="56"/>
+      <x:c r="G39" s="56"/>
+      <x:c r="H39" s="56"/>
+      <x:c r="I39" s="56"/>
+    </x:row>
+    <x:row r="40" ht="28" customHeight="1">
+      <x:c r="A40" s="59" t="str">
+        <x:v>项目版本</x:v>
+      </x:c>
+      <x:c r="B40" s="41" t="str"/>
+      <x:c r="C40" s="41" t="str"/>
+      <x:c r="D40" s="41" t="str"/>
+      <x:c r="E40" s="59" t="str">
+        <x:v>Git 提交</x:v>
+      </x:c>
+      <x:c r="F40" s="41" t="str"/>
+      <x:c r="G40" s="41" t="str"/>
+      <x:c r="H40" s="59" t="str">
+        <x:v>执行人</x:v>
+      </x:c>
+      <x:c r="I40" s="41" t="str"/>
+    </x:row>
+    <x:row r="41" ht="28" customHeight="1">
+      <x:c r="A41" s="59" t="str">
+        <x:v>操作系统</x:v>
+      </x:c>
+      <x:c r="B41" s="41" t="str"/>
+      <x:c r="C41" s="41" t="str"/>
+      <x:c r="D41" s="41" t="str"/>
+      <x:c r="E41" s="59" t="str">
+        <x:v>浏览器</x:v>
+      </x:c>
+      <x:c r="F41" s="41" t="str"/>
+      <x:c r="G41" s="41" t="str"/>
+      <x:c r="H41" s="59" t="str">
+        <x:v>执行日期</x:v>
+      </x:c>
+      <x:c r="I41" s="60"/>
+    </x:row>
+    <x:row r="42" ht="28" customHeight="1">
+      <x:c r="A42" s="59" t="str">
+        <x:v>后端入口</x:v>
+      </x:c>
+      <x:c r="B42" s="41" t="str">
+        <x:v>http://127.0.0.1:16088/health</x:v>
+      </x:c>
+      <x:c r="C42" s="41" t="str"/>
+      <x:c r="D42" s="41" t="str"/>
+      <x:c r="E42" s="59" t="str">
+        <x:v>前端入口</x:v>
+      </x:c>
+      <x:c r="F42" s="41" t="str">
+        <x:v>http://127.0.0.1:11420</x:v>
+      </x:c>
+      <x:c r="G42" s="41" t="str"/>
+      <x:c r="H42" s="59" t="str">
+        <x:v>数据库</x:v>
+      </x:c>
+      <x:c r="I42" s="41" t="str">
+        <x:v>隔离副本</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="2"/>
+      <x:c r="B43" s="2"/>
+      <x:c r="C43" s="2"/>
+      <x:c r="D43" s="2"/>
+      <x:c r="E43" s="2"/>
+      <x:c r="F43" s="2"/>
+      <x:c r="G43" s="2"/>
+      <x:c r="H43" s="2"/>
+      <x:c r="I43" s="2"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="56" t="str">
+        <x:v>运行证据清单</x:v>
+      </x:c>
+      <x:c r="B44" s="56"/>
+      <x:c r="C44" s="56"/>
+      <x:c r="D44" s="56"/>
+      <x:c r="E44" s="56"/>
+      <x:c r="F44" s="56"/>
+      <x:c r="G44" s="56"/>
+      <x:c r="H44" s="56"/>
+      <x:c r="I44" s="56"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="28" t="str">
+        <x:v>编号</x:v>
+      </x:c>
+      <x:c r="B45" s="28" t="str">
+        <x:v>运行场景</x:v>
+      </x:c>
+      <x:c r="C45" s="28"/>
+      <x:c r="D45" s="28" t="str">
+        <x:v>核验要点</x:v>
+      </x:c>
+      <x:c r="E45" s="28"/>
+      <x:c r="F45" s="28" t="str">
+        <x:v>执行结果</x:v>
+      </x:c>
+      <x:c r="G45" s="28" t="str">
+        <x:v>执行日期</x:v>
+      </x:c>
+      <x:c r="H45" s="28" t="str">
+        <x:v>执行者</x:v>
+      </x:c>
+      <x:c r="I45" s="28" t="str">
+        <x:v>截图编号/文件名</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="48" customHeight="1">
+      <x:c r="A46" s="32" t="str">
+        <x:v>S01</x:v>
+      </x:c>
+      <x:c r="B46" s="31" t="str">
+        <x:v>后端启动与健康检查</x:v>
+      </x:c>
+      <x:c r="C46" s="31"/>
+      <x:c r="D46" s="31" t="str">
+        <x:v>本地后端可启动；/health 返回成功且 data.status、data.database 均为 ok。</x:v>
+      </x:c>
+      <x:c r="E46" s="31"/>
+      <x:c r="F46" s="35" t="str">
+        <x:v>待人工执行</x:v>
+      </x:c>
+      <x:c r="G46" s="53"/>
+      <x:c r="H46" s="31" t="str"/>
+      <x:c r="I46" s="31" t="str">
+        <x:v>S01-health.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="48" customHeight="1">
+      <x:c r="A47" s="32" t="str">
+        <x:v>S02</x:v>
+      </x:c>
+      <x:c r="B47" s="31" t="str">
+        <x:v>前端入口与导航</x:v>
+      </x:c>
+      <x:c r="C47" s="31"/>
+      <x:c r="D47" s="31" t="str">
+        <x:v>浏览器工作区可加载，知识库、搜索、聊天和文档集入口可见。</x:v>
+      </x:c>
+      <x:c r="E47" s="31"/>
+      <x:c r="F47" s="35" t="str">
+        <x:v>待人工执行</x:v>
+      </x:c>
+      <x:c r="G47" s="53"/>
+      <x:c r="H47" s="31" t="str"/>
+      <x:c r="I47" s="31" t="str">
+        <x:v>S02-workspace.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="48" customHeight="1">
+      <x:c r="A48" s="32" t="str">
+        <x:v>S03</x:v>
+      </x:c>
+      <x:c r="B48" s="31" t="str">
+        <x:v>模型设置页</x:v>
+      </x:c>
+      <x:c r="C48" s="31"/>
+      <x:c r="D48" s="31" t="str">
+        <x:v>模型设置页可打开；截图不暴露密钥。未配置模型时如实记录。</x:v>
+      </x:c>
+      <x:c r="E48" s="31"/>
+      <x:c r="F48" s="35" t="str">
+        <x:v>待人工执行</x:v>
+      </x:c>
+      <x:c r="G48" s="53"/>
+      <x:c r="H48" s="31" t="str"/>
+      <x:c r="I48" s="31" t="str">
+        <x:v>S03-model-settings.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="48" customHeight="1">
+      <x:c r="A49" s="32" t="str">
+        <x:v>S04</x:v>
+      </x:c>
+      <x:c r="B49" s="31" t="str">
+        <x:v>知识库列表与详情</x:v>
+      </x:c>
+      <x:c r="C49" s="31"/>
+      <x:c r="D49" s="31" t="str">
+        <x:v>知识库页面可用；如创建测试知识库，只在隔离副本中执行。</x:v>
+      </x:c>
+      <x:c r="E49" s="31"/>
+      <x:c r="F49" s="35" t="str">
+        <x:v>待人工执行</x:v>
+      </x:c>
+      <x:c r="G49" s="53"/>
+      <x:c r="H49" s="31" t="str"/>
+      <x:c r="I49" s="31" t="str">
+        <x:v>S04-repository.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="48" customHeight="1">
+      <x:c r="A50" s="32" t="str">
+        <x:v>S05</x:v>
+      </x:c>
+      <x:c r="B50" s="31" t="str">
+        <x:v>测试资料导入与状态</x:v>
+      </x:c>
+      <x:c r="C50" s="31"/>
+      <x:c r="D50" s="31" t="str">
+        <x:v>样例文件上传后可查看数据集和真实索引状态，不将失败或未就绪写成成功。</x:v>
+      </x:c>
+      <x:c r="E50" s="31"/>
+      <x:c r="F50" s="35" t="str">
+        <x:v>待人工执行</x:v>
+      </x:c>
+      <x:c r="G50" s="53"/>
+      <x:c r="H50" s="31" t="str"/>
+      <x:c r="I50" s="31" t="str">
+        <x:v>S05-dataset.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="48" customHeight="1">
+      <x:c r="A51" s="32" t="str">
+        <x:v>S06</x:v>
+      </x:c>
+      <x:c r="B51" s="31" t="str">
+        <x:v>搜索/问答与引用（模型可用时）</x:v>
+      </x:c>
+      <x:c r="C51" s="31"/>
+      <x:c r="D51" s="31" t="str">
+        <x:v>模型和索引可用时核对命中内容及来源；依赖缺失时记录阻塞原因。</x:v>
+      </x:c>
+      <x:c r="E51" s="31"/>
+      <x:c r="F51" s="35" t="str">
+        <x:v>待人工执行</x:v>
+      </x:c>
+      <x:c r="G51" s="53"/>
+      <x:c r="H51" s="31" t="str"/>
+      <x:c r="I51" s="31" t="str">
+        <x:v>S06-search-chat.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="2"/>
+      <x:c r="B52" s="2"/>
+      <x:c r="C52" s="2"/>
+      <x:c r="D52" s="2"/>
+      <x:c r="E52" s="2"/>
+      <x:c r="F52" s="2"/>
+      <x:c r="G52" s="2"/>
+      <x:c r="H52" s="2"/>
+      <x:c r="I52" s="2"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="25" t="str">
+        <x:v>运行界面截图（完成对应步骤后粘贴；当前为空白证据位）</x:v>
+      </x:c>
+      <x:c r="B53" s="25"/>
+      <x:c r="C53" s="25"/>
+      <x:c r="D53" s="25"/>
+      <x:c r="E53" s="25"/>
+      <x:c r="F53" s="25"/>
+      <x:c r="G53" s="25"/>
+      <x:c r="H53" s="25"/>
+      <x:c r="I53" s="25"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="63" t="str">
+        <x:v>S01</x:v>
+      </x:c>
+      <x:c r="B54" s="63" t="str">
+        <x:v>后端健康检查响应</x:v>
+      </x:c>
+      <x:c r="C54" s="63"/>
+      <x:c r="D54" s="63"/>
+      <x:c r="E54" s="63"/>
+      <x:c r="F54" s="63"/>
+      <x:c r="G54" s="63"/>
+      <x:c r="H54" s="63"/>
+      <x:c r="I54" s="63"/>
+    </x:row>
+    <x:row r="55" ht="22" customHeight="1">
+      <x:c r="A55" s="74" t="str">
+        <x:v>待粘贴 S01 实际截图</x:v>
+      </x:c>
+      <x:c r="B55" s="75"/>
+      <x:c r="C55" s="75"/>
+      <x:c r="D55" s="75"/>
+      <x:c r="E55" s="75"/>
+      <x:c r="F55" s="75"/>
+      <x:c r="G55" s="75"/>
+      <x:c r="H55" s="75"/>
+      <x:c r="I55" s="76"/>
+    </x:row>
+    <x:row r="56" ht="22" customHeight="1">
+      <x:c r="A56" s="77"/>
+      <x:c r="B56" s="78"/>
+      <x:c r="C56" s="78"/>
+      <x:c r="D56" s="78"/>
+      <x:c r="E56" s="78"/>
+      <x:c r="F56" s="78"/>
+      <x:c r="G56" s="78"/>
+      <x:c r="H56" s="78"/>
+      <x:c r="I56" s="79"/>
+    </x:row>
+    <x:row r="57" ht="22" customHeight="1">
+      <x:c r="A57" s="77"/>
+      <x:c r="B57" s="78"/>
+      <x:c r="C57" s="78"/>
+      <x:c r="D57" s="78"/>
+      <x:c r="E57" s="78"/>
+      <x:c r="F57" s="78"/>
+      <x:c r="G57" s="78"/>
+      <x:c r="H57" s="78"/>
+      <x:c r="I57" s="79"/>
+    </x:row>
+    <x:row r="58" ht="22" customHeight="1">
+      <x:c r="A58" s="77"/>
+      <x:c r="B58" s="78"/>
+      <x:c r="C58" s="78"/>
+      <x:c r="D58" s="78"/>
+      <x:c r="E58" s="78"/>
+      <x:c r="F58" s="78"/>
+      <x:c r="G58" s="78"/>
+      <x:c r="H58" s="78"/>
+      <x:c r="I58" s="79"/>
+    </x:row>
+    <x:row r="59" ht="22" customHeight="1">
+      <x:c r="A59" s="77"/>
+      <x:c r="B59" s="78"/>
+      <x:c r="C59" s="78"/>
+      <x:c r="D59" s="78"/>
+      <x:c r="E59" s="78"/>
+      <x:c r="F59" s="78"/>
+      <x:c r="G59" s="78"/>
+      <x:c r="H59" s="78"/>
+      <x:c r="I59" s="79"/>
+    </x:row>
+    <x:row r="60" ht="22" customHeight="1">
+      <x:c r="A60" s="77"/>
+      <x:c r="B60" s="78"/>
+      <x:c r="C60" s="78"/>
+      <x:c r="D60" s="78"/>
+      <x:c r="E60" s="78"/>
+      <x:c r="F60" s="78"/>
+      <x:c r="G60" s="78"/>
+      <x:c r="H60" s="78"/>
+      <x:c r="I60" s="79"/>
+    </x:row>
+    <x:row r="61" ht="22" customHeight="1">
+      <x:c r="A61" s="80"/>
+      <x:c r="B61" s="81"/>
+      <x:c r="C61" s="81"/>
+      <x:c r="D61" s="81"/>
+      <x:c r="E61" s="81"/>
+      <x:c r="F61" s="81"/>
+      <x:c r="G61" s="81"/>
+      <x:c r="H61" s="81"/>
+      <x:c r="I61" s="82"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="2"/>
+      <x:c r="B62" s="2"/>
+      <x:c r="C62" s="2"/>
+      <x:c r="D62" s="2"/>
+      <x:c r="E62" s="2"/>
+      <x:c r="F62" s="2"/>
+      <x:c r="G62" s="2"/>
+      <x:c r="H62" s="2"/>
+      <x:c r="I62" s="2"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="63" t="str">
+        <x:v>S02</x:v>
+      </x:c>
+      <x:c r="B63" s="63" t="str">
+        <x:v>WenKB 浏览器工作区与主导航</x:v>
+      </x:c>
+      <x:c r="C63" s="63"/>
+      <x:c r="D63" s="63"/>
+      <x:c r="E63" s="63"/>
+      <x:c r="F63" s="63"/>
+      <x:c r="G63" s="63"/>
+      <x:c r="H63" s="63"/>
+      <x:c r="I63" s="63"/>
+    </x:row>
+    <x:row r="64" ht="22" customHeight="1">
+      <x:c r="A64" s="74" t="str">
+        <x:v>待粘贴 S02 实际截图</x:v>
+      </x:c>
+      <x:c r="B64" s="75"/>
+      <x:c r="C64" s="75"/>
+      <x:c r="D64" s="75"/>
+      <x:c r="E64" s="75"/>
+      <x:c r="F64" s="75"/>
+      <x:c r="G64" s="75"/>
+      <x:c r="H64" s="75"/>
+      <x:c r="I64" s="76"/>
+    </x:row>
+    <x:row r="65" ht="22" customHeight="1">
+      <x:c r="A65" s="77"/>
+      <x:c r="B65" s="78"/>
+      <x:c r="C65" s="78"/>
+      <x:c r="D65" s="78"/>
+      <x:c r="E65" s="78"/>
+      <x:c r="F65" s="78"/>
+      <x:c r="G65" s="78"/>
+      <x:c r="H65" s="78"/>
+      <x:c r="I65" s="79"/>
+    </x:row>
+    <x:row r="66" ht="22" customHeight="1">
+      <x:c r="A66" s="77"/>
+      <x:c r="B66" s="78"/>
+      <x:c r="C66" s="78"/>
+      <x:c r="D66" s="78"/>
+      <x:c r="E66" s="78"/>
+      <x:c r="F66" s="78"/>
+      <x:c r="G66" s="78"/>
+      <x:c r="H66" s="78"/>
+      <x:c r="I66" s="79"/>
+    </x:row>
+    <x:row r="67" ht="22" customHeight="1">
+      <x:c r="A67" s="77"/>
+      <x:c r="B67" s="78"/>
+      <x:c r="C67" s="78"/>
+      <x:c r="D67" s="78"/>
+      <x:c r="E67" s="78"/>
+      <x:c r="F67" s="78"/>
+      <x:c r="G67" s="78"/>
+      <x:c r="H67" s="78"/>
+      <x:c r="I67" s="79"/>
+    </x:row>
+    <x:row r="68" ht="22" customHeight="1">
+      <x:c r="A68" s="77"/>
+      <x:c r="B68" s="78"/>
+      <x:c r="C68" s="78"/>
+      <x:c r="D68" s="78"/>
+      <x:c r="E68" s="78"/>
+      <x:c r="F68" s="78"/>
+      <x:c r="G68" s="78"/>
+      <x:c r="H68" s="78"/>
+      <x:c r="I68" s="79"/>
+    </x:row>
+    <x:row r="69" ht="22" customHeight="1">
+      <x:c r="A69" s="77"/>
+      <x:c r="B69" s="78"/>
+      <x:c r="C69" s="78"/>
+      <x:c r="D69" s="78"/>
+      <x:c r="E69" s="78"/>
+      <x:c r="F69" s="78"/>
+      <x:c r="G69" s="78"/>
+      <x:c r="H69" s="78"/>
+      <x:c r="I69" s="79"/>
+    </x:row>
+    <x:row r="70" ht="22" customHeight="1">
+      <x:c r="A70" s="80"/>
+      <x:c r="B70" s="81"/>
+      <x:c r="C70" s="81"/>
+      <x:c r="D70" s="81"/>
+      <x:c r="E70" s="81"/>
+      <x:c r="F70" s="81"/>
+      <x:c r="G70" s="81"/>
+      <x:c r="H70" s="81"/>
+      <x:c r="I70" s="82"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="2"/>
+      <x:c r="B71" s="2"/>
+      <x:c r="C71" s="2"/>
+      <x:c r="D71" s="2"/>
+      <x:c r="E71" s="2"/>
+      <x:c r="F71" s="2"/>
+      <x:c r="G71" s="2"/>
+      <x:c r="H71" s="2"/>
+      <x:c r="I71" s="2"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="63" t="str">
+        <x:v>S03</x:v>
+      </x:c>
+      <x:c r="B72" s="63" t="str">
+        <x:v>模型设置页面（凭据已脱敏或未配置）</x:v>
+      </x:c>
+      <x:c r="C72" s="63"/>
+      <x:c r="D72" s="63"/>
+      <x:c r="E72" s="63"/>
+      <x:c r="F72" s="63"/>
+      <x:c r="G72" s="63"/>
+      <x:c r="H72" s="63"/>
+      <x:c r="I72" s="63"/>
+    </x:row>
+    <x:row r="73" ht="22" customHeight="1">
+      <x:c r="A73" s="74" t="str">
+        <x:v>待粘贴 S03 实际截图</x:v>
+      </x:c>
+      <x:c r="B73" s="75"/>
+      <x:c r="C73" s="75"/>
+      <x:c r="D73" s="75"/>
+      <x:c r="E73" s="75"/>
+      <x:c r="F73" s="75"/>
+      <x:c r="G73" s="75"/>
+      <x:c r="H73" s="75"/>
+      <x:c r="I73" s="76"/>
+    </x:row>
+    <x:row r="74" ht="22" customHeight="1">
+      <x:c r="A74" s="77"/>
+      <x:c r="B74" s="78"/>
+      <x:c r="C74" s="78"/>
+      <x:c r="D74" s="78"/>
+      <x:c r="E74" s="78"/>
+      <x:c r="F74" s="78"/>
+      <x:c r="G74" s="78"/>
+      <x:c r="H74" s="78"/>
+      <x:c r="I74" s="79"/>
+    </x:row>
+    <x:row r="75" ht="22" customHeight="1">
+      <x:c r="A75" s="77"/>
+      <x:c r="B75" s="78"/>
+      <x:c r="C75" s="78"/>
+      <x:c r="D75" s="78"/>
+      <x:c r="E75" s="78"/>
+      <x:c r="F75" s="78"/>
+      <x:c r="G75" s="78"/>
+      <x:c r="H75" s="78"/>
+      <x:c r="I75" s="79"/>
+    </x:row>
+    <x:row r="76" ht="22" customHeight="1">
+      <x:c r="A76" s="77"/>
+      <x:c r="B76" s="78"/>
+      <x:c r="C76" s="78"/>
+      <x:c r="D76" s="78"/>
+      <x:c r="E76" s="78"/>
+      <x:c r="F76" s="78"/>
+      <x:c r="G76" s="78"/>
+      <x:c r="H76" s="78"/>
+      <x:c r="I76" s="79"/>
+    </x:row>
+    <x:row r="77" ht="22" customHeight="1">
+      <x:c r="A77" s="77"/>
+      <x:c r="B77" s="78"/>
+      <x:c r="C77" s="78"/>
+      <x:c r="D77" s="78"/>
+      <x:c r="E77" s="78"/>
+      <x:c r="F77" s="78"/>
+      <x:c r="G77" s="78"/>
+      <x:c r="H77" s="78"/>
+      <x:c r="I77" s="79"/>
+    </x:row>
+    <x:row r="78" ht="22" customHeight="1">
+      <x:c r="A78" s="77"/>
+      <x:c r="B78" s="78"/>
+      <x:c r="C78" s="78"/>
+      <x:c r="D78" s="78"/>
+      <x:c r="E78" s="78"/>
+      <x:c r="F78" s="78"/>
+      <x:c r="G78" s="78"/>
+      <x:c r="H78" s="78"/>
+      <x:c r="I78" s="79"/>
+    </x:row>
+    <x:row r="79" ht="22" customHeight="1">
+      <x:c r="A79" s="80"/>
+      <x:c r="B79" s="81"/>
+      <x:c r="C79" s="81"/>
+      <x:c r="D79" s="81"/>
+      <x:c r="E79" s="81"/>
+      <x:c r="F79" s="81"/>
+      <x:c r="G79" s="81"/>
+      <x:c r="H79" s="81"/>
+      <x:c r="I79" s="82"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="2"/>
+      <x:c r="B80" s="2"/>
+      <x:c r="C80" s="2"/>
+      <x:c r="D80" s="2"/>
+      <x:c r="E80" s="2"/>
+      <x:c r="F80" s="2"/>
+      <x:c r="G80" s="2"/>
+      <x:c r="H80" s="2"/>
+      <x:c r="I80" s="2"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="63" t="str">
+        <x:v>S04</x:v>
+      </x:c>
+      <x:c r="B81" s="63" t="str">
+        <x:v>隔离测试知识库列表或详情</x:v>
+      </x:c>
+      <x:c r="C81" s="63"/>
+      <x:c r="D81" s="63"/>
+      <x:c r="E81" s="63"/>
+      <x:c r="F81" s="63"/>
+      <x:c r="G81" s="63"/>
+      <x:c r="H81" s="63"/>
+      <x:c r="I81" s="63"/>
+    </x:row>
+    <x:row r="82" ht="22" customHeight="1">
+      <x:c r="A82" s="74" t="str">
+        <x:v>待粘贴 S04 实际截图</x:v>
+      </x:c>
+      <x:c r="B82" s="75"/>
+      <x:c r="C82" s="75"/>
+      <x:c r="D82" s="75"/>
+      <x:c r="E82" s="75"/>
+      <x:c r="F82" s="75"/>
+      <x:c r="G82" s="75"/>
+      <x:c r="H82" s="75"/>
+      <x:c r="I82" s="76"/>
+    </x:row>
+    <x:row r="83" ht="22" customHeight="1">
+      <x:c r="A83" s="77"/>
+      <x:c r="B83" s="78"/>
+      <x:c r="C83" s="78"/>
+      <x:c r="D83" s="78"/>
+      <x:c r="E83" s="78"/>
+      <x:c r="F83" s="78"/>
+      <x:c r="G83" s="78"/>
+      <x:c r="H83" s="78"/>
+      <x:c r="I83" s="79"/>
+    </x:row>
+    <x:row r="84" ht="22" customHeight="1">
+      <x:c r="A84" s="77"/>
+      <x:c r="B84" s="78"/>
+      <x:c r="C84" s="78"/>
+      <x:c r="D84" s="78"/>
+      <x:c r="E84" s="78"/>
+      <x:c r="F84" s="78"/>
+      <x:c r="G84" s="78"/>
+      <x:c r="H84" s="78"/>
+      <x:c r="I84" s="79"/>
+    </x:row>
+    <x:row r="85" ht="22" customHeight="1">
+      <x:c r="A85" s="77"/>
+      <x:c r="B85" s="78"/>
+      <x:c r="C85" s="78"/>
+      <x:c r="D85" s="78"/>
+      <x:c r="E85" s="78"/>
+      <x:c r="F85" s="78"/>
+      <x:c r="G85" s="78"/>
+      <x:c r="H85" s="78"/>
+      <x:c r="I85" s="79"/>
+    </x:row>
+    <x:row r="86" ht="22" customHeight="1">
+      <x:c r="A86" s="77"/>
+      <x:c r="B86" s="78"/>
+      <x:c r="C86" s="78"/>
+      <x:c r="D86" s="78"/>
+      <x:c r="E86" s="78"/>
+      <x:c r="F86" s="78"/>
+      <x:c r="G86" s="78"/>
+      <x:c r="H86" s="78"/>
+      <x:c r="I86" s="79"/>
+    </x:row>
+    <x:row r="87" ht="22" customHeight="1">
+      <x:c r="A87" s="77"/>
+      <x:c r="B87" s="78"/>
+      <x:c r="C87" s="78"/>
+      <x:c r="D87" s="78"/>
+      <x:c r="E87" s="78"/>
+      <x:c r="F87" s="78"/>
+      <x:c r="G87" s="78"/>
+      <x:c r="H87" s="78"/>
+      <x:c r="I87" s="79"/>
+    </x:row>
+    <x:row r="88" ht="22" customHeight="1">
+      <x:c r="A88" s="80"/>
+      <x:c r="B88" s="81"/>
+      <x:c r="C88" s="81"/>
+      <x:c r="D88" s="81"/>
+      <x:c r="E88" s="81"/>
+      <x:c r="F88" s="81"/>
+      <x:c r="G88" s="81"/>
+      <x:c r="H88" s="81"/>
+      <x:c r="I88" s="82"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="2"/>
+      <x:c r="B89" s="2"/>
+      <x:c r="C89" s="2"/>
+      <x:c r="D89" s="2"/>
+      <x:c r="E89" s="2"/>
+      <x:c r="F89" s="2"/>
+      <x:c r="G89" s="2"/>
+      <x:c r="H89" s="2"/>
+      <x:c r="I89" s="2"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="63" t="str">
+        <x:v>S05</x:v>
+      </x:c>
+      <x:c r="B90" s="63" t="str">
+        <x:v>测试资料导入结果与数据集状态</x:v>
+      </x:c>
+      <x:c r="C90" s="63"/>
+      <x:c r="D90" s="63"/>
+      <x:c r="E90" s="63"/>
+      <x:c r="F90" s="63"/>
+      <x:c r="G90" s="63"/>
+      <x:c r="H90" s="63"/>
+      <x:c r="I90" s="63"/>
+    </x:row>
+    <x:row r="91" ht="22" customHeight="1">
+      <x:c r="A91" s="74" t="str">
+        <x:v>待粘贴 S05 实际截图</x:v>
+      </x:c>
+      <x:c r="B91" s="75"/>
+      <x:c r="C91" s="75"/>
+      <x:c r="D91" s="75"/>
+      <x:c r="E91" s="75"/>
+      <x:c r="F91" s="75"/>
+      <x:c r="G91" s="75"/>
+      <x:c r="H91" s="75"/>
+      <x:c r="I91" s="76"/>
+    </x:row>
+    <x:row r="92" ht="22" customHeight="1">
+      <x:c r="A92" s="77"/>
+      <x:c r="B92" s="78"/>
+      <x:c r="C92" s="78"/>
+      <x:c r="D92" s="78"/>
+      <x:c r="E92" s="78"/>
+      <x:c r="F92" s="78"/>
+      <x:c r="G92" s="78"/>
+      <x:c r="H92" s="78"/>
+      <x:c r="I92" s="79"/>
+    </x:row>
+    <x:row r="93" ht="22" customHeight="1">
+      <x:c r="A93" s="77"/>
+      <x:c r="B93" s="78"/>
+      <x:c r="C93" s="78"/>
+      <x:c r="D93" s="78"/>
+      <x:c r="E93" s="78"/>
+      <x:c r="F93" s="78"/>
+      <x:c r="G93" s="78"/>
+      <x:c r="H93" s="78"/>
+      <x:c r="I93" s="79"/>
+    </x:row>
+    <x:row r="94" ht="22" customHeight="1">
+      <x:c r="A94" s="77"/>
+      <x:c r="B94" s="78"/>
+      <x:c r="C94" s="78"/>
+      <x:c r="D94" s="78"/>
+      <x:c r="E94" s="78"/>
+      <x:c r="F94" s="78"/>
+      <x:c r="G94" s="78"/>
+      <x:c r="H94" s="78"/>
+      <x:c r="I94" s="79"/>
+    </x:row>
+    <x:row r="95" ht="22" customHeight="1">
+      <x:c r="A95" s="77"/>
+      <x:c r="B95" s="78"/>
+      <x:c r="C95" s="78"/>
+      <x:c r="D95" s="78"/>
+      <x:c r="E95" s="78"/>
+      <x:c r="F95" s="78"/>
+      <x:c r="G95" s="78"/>
+      <x:c r="H95" s="78"/>
+      <x:c r="I95" s="79"/>
+    </x:row>
+    <x:row r="96" ht="22" customHeight="1">
+      <x:c r="A96" s="77"/>
+      <x:c r="B96" s="78"/>
+      <x:c r="C96" s="78"/>
+      <x:c r="D96" s="78"/>
+      <x:c r="E96" s="78"/>
+      <x:c r="F96" s="78"/>
+      <x:c r="G96" s="78"/>
+      <x:c r="H96" s="78"/>
+      <x:c r="I96" s="79"/>
+    </x:row>
+    <x:row r="97" ht="22" customHeight="1">
+      <x:c r="A97" s="80"/>
+      <x:c r="B97" s="81"/>
+      <x:c r="C97" s="81"/>
+      <x:c r="D97" s="81"/>
+      <x:c r="E97" s="81"/>
+      <x:c r="F97" s="81"/>
+      <x:c r="G97" s="81"/>
+      <x:c r="H97" s="81"/>
+      <x:c r="I97" s="82"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="2"/>
+      <x:c r="B98" s="2"/>
+      <x:c r="C98" s="2"/>
+      <x:c r="D98" s="2"/>
+      <x:c r="E98" s="2"/>
+      <x:c r="F98" s="2"/>
+      <x:c r="G98" s="2"/>
+      <x:c r="H98" s="2"/>
+      <x:c r="I98" s="2"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="63" t="str">
+        <x:v>S06</x:v>
+      </x:c>
+      <x:c r="B99" s="63" t="str">
+        <x:v>搜索/问答结果及引用；模型不可用时改贴阻塞现象</x:v>
+      </x:c>
+      <x:c r="C99" s="63"/>
+      <x:c r="D99" s="63"/>
+      <x:c r="E99" s="63"/>
+      <x:c r="F99" s="63"/>
+      <x:c r="G99" s="63"/>
+      <x:c r="H99" s="63"/>
+      <x:c r="I99" s="63"/>
+    </x:row>
+    <x:row r="100" ht="22" customHeight="1">
+      <x:c r="A100" s="74" t="str">
+        <x:v>待粘贴 S06 实际截图</x:v>
+      </x:c>
+      <x:c r="B100" s="75"/>
+      <x:c r="C100" s="75"/>
+      <x:c r="D100" s="75"/>
+      <x:c r="E100" s="75"/>
+      <x:c r="F100" s="75"/>
+      <x:c r="G100" s="75"/>
+      <x:c r="H100" s="75"/>
+      <x:c r="I100" s="76"/>
+    </x:row>
+    <x:row r="101" ht="22" customHeight="1">
+      <x:c r="A101" s="77"/>
+      <x:c r="B101" s="78"/>
+      <x:c r="C101" s="78"/>
+      <x:c r="D101" s="78"/>
+      <x:c r="E101" s="78"/>
+      <x:c r="F101" s="78"/>
+      <x:c r="G101" s="78"/>
+      <x:c r="H101" s="78"/>
+      <x:c r="I101" s="79"/>
+    </x:row>
+    <x:row r="102" ht="22" customHeight="1">
+      <x:c r="A102" s="77"/>
+      <x:c r="B102" s="78"/>
+      <x:c r="C102" s="78"/>
+      <x:c r="D102" s="78"/>
+      <x:c r="E102" s="78"/>
+      <x:c r="F102" s="78"/>
+      <x:c r="G102" s="78"/>
+      <x:c r="H102" s="78"/>
+      <x:c r="I102" s="79"/>
+    </x:row>
+    <x:row r="103" ht="22" customHeight="1">
+      <x:c r="A103" s="77"/>
+      <x:c r="B103" s="78"/>
+      <x:c r="C103" s="78"/>
+      <x:c r="D103" s="78"/>
+      <x:c r="E103" s="78"/>
+      <x:c r="F103" s="78"/>
+      <x:c r="G103" s="78"/>
+      <x:c r="H103" s="78"/>
+      <x:c r="I103" s="79"/>
+    </x:row>
+    <x:row r="104" ht="22" customHeight="1">
+      <x:c r="A104" s="77"/>
+      <x:c r="B104" s="78"/>
+      <x:c r="C104" s="78"/>
+      <x:c r="D104" s="78"/>
+      <x:c r="E104" s="78"/>
+      <x:c r="F104" s="78"/>
+      <x:c r="G104" s="78"/>
+      <x:c r="H104" s="78"/>
+      <x:c r="I104" s="79"/>
+    </x:row>
+    <x:row r="105" ht="22" customHeight="1">
+      <x:c r="A105" s="77"/>
+      <x:c r="B105" s="78"/>
+      <x:c r="C105" s="78"/>
+      <x:c r="D105" s="78"/>
+      <x:c r="E105" s="78"/>
+      <x:c r="F105" s="78"/>
+      <x:c r="G105" s="78"/>
+      <x:c r="H105" s="78"/>
+      <x:c r="I105" s="79"/>
+    </x:row>
+    <x:row r="106" ht="22" customHeight="1">
+      <x:c r="A106" s="80"/>
+      <x:c r="B106" s="81"/>
+      <x:c r="C106" s="81"/>
+      <x:c r="D106" s="81"/>
+      <x:c r="E106" s="81"/>
+      <x:c r="F106" s="81"/>
+      <x:c r="G106" s="81"/>
+      <x:c r="H106" s="81"/>
+      <x:c r="I106" s="82"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A1:I1"/>
     <x:mergeCell ref="A21:H21"/>
     <x:mergeCell ref="B22:H22"/>
     <x:mergeCell ref="B23:H23"/>
     <x:mergeCell ref="B24:H24"/>
     <x:mergeCell ref="B25:H25"/>
     <x:mergeCell ref="B26:H26"/>
+    <x:mergeCell ref="A36:I36"/>
+    <x:mergeCell ref="A37:I37"/>
+    <x:mergeCell ref="A39:I39"/>
+    <x:mergeCell ref="B40:D40"/>
+    <x:mergeCell ref="F40:G40"/>
+    <x:mergeCell ref="B41:D41"/>
+    <x:mergeCell ref="F41:G41"/>
+    <x:mergeCell ref="B42:D42"/>
+    <x:mergeCell ref="F42:G42"/>
+    <x:mergeCell ref="A44:I44"/>
+    <x:mergeCell ref="B45:C45"/>
+    <x:mergeCell ref="D45:E45"/>
+    <x:mergeCell ref="B46:C46"/>
+    <x:mergeCell ref="D46:E46"/>
+    <x:mergeCell ref="B47:C47"/>
+    <x:mergeCell ref="D47:E47"/>
+    <x:mergeCell ref="B48:C48"/>
+    <x:mergeCell ref="D48:E48"/>
+    <x:mergeCell ref="B49:C49"/>
+    <x:mergeCell ref="D49:E49"/>
+    <x:mergeCell ref="B50:C50"/>
+    <x:mergeCell ref="D50:E50"/>
+    <x:mergeCell ref="B51:C51"/>
+    <x:mergeCell ref="D51:E51"/>
+    <x:mergeCell ref="A53:I53"/>
+    <x:mergeCell ref="B54:I54"/>
+    <x:mergeCell ref="B63:I63"/>
+    <x:mergeCell ref="B72:I72"/>
+    <x:mergeCell ref="B81:I81"/>
+    <x:mergeCell ref="B90:I90"/>
+    <x:mergeCell ref="B99:I99"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="B11:B11">
     <x:cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThan">
@@ -3785,14 +4999,22 @@
       <x:formula>0</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:dataValidations count="1">
+  <x:conditionalFormatting sqref="F46:F51">
+    <x:cfRule type="containsText" dxfId="9" priority="6" operator="containsText" text="通过"/>
+    <x:cfRule type="containsText" dxfId="10" priority="7" operator="containsText" text="失败"/>
+    <x:cfRule type="containsText" dxfId="11" priority="8" operator="containsText" text="阻塞"/>
+  </x:conditionalFormatting>
+  <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="C30:C34">
       <x:formula1>"高,中,低"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="F46:F51">
+      <x:formula1>"待人工执行,通过,失败,阻塞,不适用"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5f385c3f1fd41e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R132dae3e76ab429c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/wenkb-test-book-in-progress/第14小组_基于大模型的个人知识库系统_测试成绩书.xlsx
+++ b/outputs/wenkb-test-book-in-progress/第14小组_基于大模型的个人知识库系统_测试成绩书.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文件封面" sheetId="1" r:id="R4ad4a0728dd34645"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试项目" sheetId="2" r:id="R3d94d4b9f5554adc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI界面" sheetId="3" r:id="R5b5654dcb3fc4be3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="运行" sheetId="4" r:id="Rccbcec2a52a7457f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文件封面" sheetId="1" r:id="R91a995105a9d4dea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试项目" sheetId="2" r:id="R9c08248263c645bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI界面" sheetId="3" r:id="Rc866cfea6b9b4f05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="运行" sheetId="4" r:id="Re06a044b7ef64a4e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -501,7 +501,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -512,7 +512,7 @@
         <x:color rgb="FF375623"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -523,7 +523,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -534,7 +534,7 @@
         <x:color rgb="FF9C6500"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -545,7 +545,7 @@
         <x:color rgb="FF375623"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -556,7 +556,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -567,7 +567,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -578,7 +578,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -589,7 +589,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -600,7 +600,7 @@
         <x:color rgb="FF375623"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -611,7 +611,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -622,7 +622,7 @@
         <x:color rgb="FF9C6500"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -1017,7 +1017,7 @@
         <x:v>文档状态</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>执行前草案</x:v>
+        <x:v>执行记录已回填，截图待人工补充</x:v>
       </x:c>
       <x:c r="C14" s="2"/>
       <x:c r="D14" s="2"/>
@@ -1069,7 +1069,7 @@
         <x:v>执行状态</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>未执行，待填写</x:v>
+        <x:v>14 通过，8 失败，26 阻塞；截图待人工补充</x:v>
       </x:c>
       <x:c r="C18" s="2"/>
       <x:c r="D18" s="2"/>
@@ -1108,7 +1108,7 @@
     </x:row>
     <x:row r="22" ht="42" customHeight="1">
       <x:c r="A22" s="14" t="str">
-        <x:v>本成绩书依据需求分析、详细设计、接口设计、操作手册和测试计划整理。执行结果不得预填；每条用例执行后应补充实测结果、状态、日期、测试者和证据。</x:v>
+        <x:v>本成绩书依据需求分析、详细设计、接口设计、操作手册和测试计划整理。执行结果按实际记录；失败和阻塞项均保留现象、前置条件及缺陷编号。</x:v>
       </x:c>
       <x:c r="B22" s="14"/>
       <x:c r="C22" s="14"/>
@@ -1438,15 +1438,22 @@
       <x:c r="G5" s="31" t="str">
         <x:v>正常条件返回明确健康状态；数据库不可用时返回可识别失败状态，不输出敏感配置。</x:v>
       </x:c>
-      <x:c r="H5" s="32" t="str"/>
+      <x:c r="H5" s="32" t="str">
+        <x:v>GET /health 返回 HTTP 200；success=true、status=ok、database=ok。</x:v>
+      </x:c>
       <x:c r="I5" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J5" s="33"/>
-      <x:c r="K5" s="31" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="J5" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K5" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L5" s="31" t="str"/>
       <x:c r="M5" s="31" t="str">
-        <x:v>记录 HTTP 状态、响应摘要和服务日志编号。</x:v>
+        <x:v>记录 HTTP 状态、响应摘要和服务日志编号。
+执行证据：隔离后端 HTTP 响应。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="78" customHeight="1">
@@ -1475,15 +1482,22 @@
       <x:c r="G6" s="31" t="str">
         <x:v>服务可用时页面可进入；后端不可达时显示明确错误或重试状态，不把连接失败显示为正常。</x:v>
       </x:c>
-      <x:c r="H6" s="32" t="str"/>
+      <x:c r="H6" s="32" t="str">
+        <x:v>Vite 入口和 /api/health 代理返回 HTTP 200；浏览器实际交互、后端断开反馈及 Tauri 入口未核验。</x:v>
+      </x:c>
       <x:c r="I6" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J6" s="33"/>
-      <x:c r="K6" s="31" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="J6" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K6" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L6" s="31" t="str"/>
       <x:c r="M6" s="31" t="str">
-        <x:v>记录浏览器/桌面端入口及连接状态截图。</x:v>
+        <x:v>记录浏览器/桌面端入口及连接状态截图。
+执行证据：Vite 开发服务器与 HTTP 响应；界面留待人工截图。</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="78" customHeight="1">
@@ -1512,15 +1526,22 @@
       <x:c r="G7" s="31" t="str">
         <x:v>迁移按版本顺序完成；版本号更新；重启不重复破坏数据；失败时保留可追踪错误。</x:v>
       </x:c>
-      <x:c r="H7" s="32" t="str"/>
+      <x:c r="H7" s="32" t="str">
+        <x:v>隔离数据库首次升至 schema v5；服务重启后仍为 v5，原测试数据保留。</x:v>
+      </x:c>
       <x:c r="I7" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J7" s="33"/>
-      <x:c r="K7" s="31" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="J7" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K7" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L7" s="31" t="str"/>
       <x:c r="M7" s="31" t="str">
-        <x:v>仅在副本执行，保存迁移日志及升级前后记录数量。</x:v>
+        <x:v>仅在副本执行，保存迁移日志及升级前后记录数量。
+执行证据：隔离 SQLite schema version 前后查询及启动日志。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="78" customHeight="1">
@@ -1549,15 +1570,22 @@
       <x:c r="G8" s="31" t="str">
         <x:v>文件路径可读写；导入记录可追溯；中文文件名和目录名不导致服务异常。</x:v>
       </x:c>
-      <x:c r="H8" s="32" t="str"/>
+      <x:c r="H8" s="32" t="str">
+        <x:v>API 保留中文文件名；本次服务数据目录为 ASCII 路径，未验证中文目录读写及索引。</x:v>
+      </x:c>
       <x:c r="I8" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J8" s="33"/>
-      <x:c r="K8" s="31" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="J8" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K8" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L8" s="31" t="str"/>
       <x:c r="M8" s="31" t="str">
-        <x:v>记录测试文件名和数据集 ID，不复制敏感文件内容。</x:v>
+        <x:v>记录测试文件名和数据集 ID，不复制敏感文件内容。
+执行证据：中文文件名上传记录；中文路径样本未执行。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="78" customHeight="1">
@@ -1586,15 +1614,22 @@
       <x:c r="G9" s="31" t="str">
         <x:v>供应商和模型列表可查询；新增模型保存后可重新读取；聊天模型和 embedding 模型按类型区分。</x:v>
       </x:c>
-      <x:c r="H9" s="32" t="str"/>
+      <x:c r="H9" s="32" t="str">
+        <x:v>供应商清单可读；测试模型可新增、列表读取并删除。</x:v>
+      </x:c>
       <x:c r="I9" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J9" s="33"/>
-      <x:c r="K9" s="31" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="J9" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K9" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L9" s="31" t="str"/>
       <x:c r="M9" s="31" t="str">
-        <x:v>记录供应商、模型 ID 和模型类型。</x:v>
+        <x:v>记录供应商、模型 ID 和模型类型。
+执行证据：模型配置 API 请求与临时记录清理。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="78" customHeight="1">
@@ -1623,15 +1658,22 @@
       <x:c r="G10" s="31" t="str">
         <x:v>参数保存成功；敏感值加密保存；查询或界面回显不暴露完整 API Key。</x:v>
       </x:c>
-      <x:c r="H10" s="32" t="str"/>
+      <x:c r="H10" s="32" t="str">
+        <x:v>使用虚构测试值验证加密保存和回读脱敏；未使用真实 API Key。</x:v>
+      </x:c>
       <x:c r="I10" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J10" s="33"/>
-      <x:c r="K10" s="31" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="J10" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K10" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L10" s="31" t="str"/>
       <x:c r="M10" s="31" t="str">
-        <x:v>记录脱敏格式和参数加密状态，不记录真实密钥。</x:v>
+        <x:v>记录脱敏格式和参数加密状态，不记录真实密钥。
+执行证据：参数 API 回读掩码；测试值未保留在隔离库之外。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="78" customHeight="1">
@@ -1660,15 +1702,22 @@
       <x:c r="G11" s="31" t="str">
         <x:v>保存的默认模型在后续问答/增强中生效；切换后使用新选择，模型调用结果可追踪。</x:v>
       </x:c>
-      <x:c r="H11" s="32" t="str"/>
+      <x:c r="H11" s="32" t="str">
+        <x:v>没有真实 LLM 服务或专用凭据，未能验证切换默认模型后由指定模型实际完成调用。</x:v>
+      </x:c>
       <x:c r="I11" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J11" s="33"/>
-      <x:c r="K11" s="31" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="J11" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K11" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L11" s="31" t="str"/>
       <x:c r="M11" s="31" t="str">
-        <x:v>用服务日志或可控模型响应确认实际调用模型。</x:v>
+        <x:v>用服务日志或可控模型响应确认实际调用模型。
+执行证据：无模型服务；没有发起外部凭据调用。</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="78" customHeight="1">
@@ -1697,15 +1746,24 @@
       <x:c r="G12" s="31" t="str">
         <x:v>系统明确提示模型未配置或不可用；失败上下文可追踪；API Key 等敏感值不进入错误信息。</x:v>
       </x:c>
-      <x:c r="H12" s="32" t="str"/>
+      <x:c r="H12" s="32" t="str">
+        <x:v>未配置模型时 SSE 返回明确设置提示和兜底文本且未泄漏凭据；助手兜底消息未写入历史消息，见 DEF-WKB-005。</x:v>
+      </x:c>
       <x:c r="I12" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J12" s="33"/>
-      <x:c r="K12" s="31" t="str"/>
-      <x:c r="L12" s="31" t="str"/>
+        <x:v>失败</x:v>
+      </x:c>
+      <x:c r="J12" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K12" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
+      <x:c r="L12" s="31" t="str">
+        <x:v>DEF-WKB-005</x:v>
+      </x:c>
       <x:c r="M12" s="31" t="str">
-        <x:v>记录错误类型、用户提示和日志编号。</x:v>
+        <x:v>记录错误类型、用户提示和日志编号。
+执行证据：隔离聊天 SSE 响应及消息列表 API。</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="78" customHeight="1">
@@ -1734,15 +1792,22 @@
       <x:c r="G13" s="31" t="str">
         <x:v>知识库创建成功并绑定所选 embedding 模型；新建知识库默认私有；详情可重新读取。</x:v>
       </x:c>
-      <x:c r="H13" s="32" t="str"/>
+      <x:c r="H13" s="32" t="str">
+        <x:v>知识库创建成功；embedding 模型 ID 被保存，authRang 默认为 prvt，问答设置可重读。</x:v>
+      </x:c>
       <x:c r="I13" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J13" s="33"/>
-      <x:c r="K13" s="31" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="J13" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K13" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L13" s="31" t="str"/>
       <x:c r="M13" s="31" t="str">
-        <x:v>记录知识库 ID、模型 ID 和权限范围。</x:v>
+        <x:v>记录知识库 ID、模型 ID 和权限范围。
+执行证据：隔离知识库及设置 API。</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="78" customHeight="1">
@@ -1771,15 +1836,24 @@
       <x:c r="G14" s="31" t="str">
         <x:v>缺少必填项时拒绝创建并给出明确提示；不产生名称或索引模型缺失的知识库。</x:v>
       </x:c>
-      <x:c r="H14" s="32" t="str"/>
+      <x:c r="H14" s="32" t="str">
+        <x:v>缺少 embedding 模型会返回 HTTP 400；空知识库名称仍返回 HTTP 200 并创建记录，见 DEF-WKB-002。</x:v>
+      </x:c>
       <x:c r="I14" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J14" s="33"/>
-      <x:c r="K14" s="31" t="str"/>
-      <x:c r="L14" s="31" t="str"/>
+        <x:v>失败</x:v>
+      </x:c>
+      <x:c r="J14" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K14" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
+      <x:c r="L14" s="31" t="str">
+        <x:v>DEF-WKB-002</x:v>
+      </x:c>
       <x:c r="M14" s="31" t="str">
-        <x:v>记录每种输入的提示和保存结果。</x:v>
+        <x:v>记录每种输入的提示和保存结果。
+执行证据：隔离知识库创建 API；空名称记录留在临时数据库。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="78" customHeight="1">
@@ -1808,15 +1882,22 @@
       <x:c r="G15" s="31" t="str">
         <x:v>合法范围值可保存并在重新读取后保持一致；越界值被校验；后续问答使用已保存参数。</x:v>
       </x:c>
-      <x:c r="H15" s="32" t="str"/>
+      <x:c r="H15" s="32" t="str">
+        <x:v>maxCtx、maxHist、temperature、similarity 和 topK 可保存并重读；设计基线没有定义合法数值边界，本次未判边界校验。</x:v>
+      </x:c>
       <x:c r="I15" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J15" s="33"/>
-      <x:c r="K15" s="31" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="J15" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K15" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L15" s="31" t="str"/>
       <x:c r="M15" s="31" t="str">
-        <x:v>记录输入边界、保存值和请求侧验证结果。</x:v>
+        <x:v>记录输入边界、保存值和请求侧验证结果。
+执行证据：隔离知识库设置 API。</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="78" customHeight="1">
@@ -1845,15 +1926,22 @@
       <x:c r="G16" s="31" t="str">
         <x:v>模型不一致风险被提示；确认切换后触发或要求重建；取消时不破坏原有可检索索引。</x:v>
       </x:c>
-      <x:c r="H16" s="32" t="str"/>
+      <x:c r="H16" s="32" t="str">
+        <x:v>将隔离测试数据临时设为 ready 后切换 embedding 返回 HTTP 409，原模型 ID 未变；测试状态已还原。</x:v>
+      </x:c>
       <x:c r="I16" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J16" s="33"/>
-      <x:c r="K16" s="31" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="J16" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K16" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L16" s="31" t="str"/>
       <x:c r="M16" s="31" t="str">
-        <x:v>保存切换前后模型 ID、提示和索引状态。</x:v>
+        <x:v>保存切换前后模型 ID、提示和索引状态。
+执行证据：隔离数据库状态变更和知识库编辑 API。</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="78" customHeight="1">
@@ -1882,15 +1970,22 @@
       <x:c r="G17" s="31" t="str">
         <x:v>需求范围内的常见格式建立正确数据集记录；不支持或无法解析的样本显示失败原因，不显示为 ready。</x:v>
       </x:c>
-      <x:c r="H17" s="32" t="str"/>
+      <x:c r="H17" s="32" t="str">
+        <x:v>PDF、DOCX、MD、TXT、PPTX 上传入口接受样本；由于没有 embedding 权重，未验证有效文件解析和索引。占位二进制不作为格式通过证据。</x:v>
+      </x:c>
       <x:c r="I17" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J17" s="33"/>
-      <x:c r="K17" s="31" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="J17" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K17" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L17" s="31" t="str"/>
       <x:c r="M17" s="31" t="str">
-        <x:v>记录样本格式、文件 ID 和数据集 ID。</x:v>
+        <x:v>记录样本格式、文件 ID 和数据集 ID。
+执行证据：隔离上传 API；模型资源缺失。</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="78" customHeight="1">
@@ -1919,15 +2014,22 @@
       <x:c r="G18" s="31" t="str">
         <x:v>批量结果可逐项追踪；同名文件不会静默覆盖另一文件；失败项不会被汇总成成功状态。</x:v>
       </x:c>
-      <x:c r="H18" s="32" t="str"/>
+      <x:c r="H18" s="32" t="str">
+        <x:v>同名文件两次上传获得不同 dtsetId，并分别写入不同文件路径。</x:v>
+      </x:c>
       <x:c r="I18" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J18" s="33"/>
-      <x:c r="K18" s="31" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="J18" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K18" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L18" s="31" t="str"/>
       <x:c r="M18" s="31" t="str">
-        <x:v>保留上传响应摘要和同名样本的区分方式。</x:v>
+        <x:v>保留上传响应摘要和同名样本的区分方式。
+执行证据：隔离数据集列表与文件路径查询。</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="78" customHeight="1">
@@ -1956,15 +2058,24 @@
       <x:c r="G19" s="31" t="str">
         <x:v>有效 URL 可保存并尽力获取标题；格式错误 URL 被识别；链接和数据集关系可重新查询。</x:v>
       </x:c>
-      <x:c r="H19" s="32" t="str"/>
+      <x:c r="H19" s="32" t="str">
+        <x:v>格式错误值 not-a-valid-url 被 HTTP 200 接受并保存为链接数据集，见 DEF-WKB-003。</x:v>
+      </x:c>
       <x:c r="I19" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J19" s="33"/>
-      <x:c r="K19" s="31" t="str"/>
-      <x:c r="L19" s="31" t="str"/>
+        <x:v>失败</x:v>
+      </x:c>
+      <x:c r="J19" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K19" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
+      <x:c r="L19" s="31" t="str">
+        <x:v>DEF-WKB-003</x:v>
+      </x:c>
       <x:c r="M19" s="31" t="str">
-        <x:v>记录 URL 测试编号、标题和数据集 ID，不记录需授权访问的私有链接。</x:v>
+        <x:v>记录 URL 测试编号、标题和数据集 ID，不记录需授权访问的私有链接。
+执行证据：隔离链接导入 API。</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="78" customHeight="1">
@@ -1993,15 +2104,22 @@
       <x:c r="G20" s="31" t="str">
         <x:v>异常样本失败原因可查询且不会变为 ready；单个异常不导致服务整体退出或阻断其他数据集。</x:v>
       </x:c>
-      <x:c r="H20" s="32" t="str"/>
+      <x:c r="H20" s="32" t="str">
+        <x:v>损坏文件和不可访问链接未进入可判断的解析/索引流程；无法验证失败状态及其他正常数据集隔离。</x:v>
+      </x:c>
       <x:c r="I20" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J20" s="33"/>
-      <x:c r="K20" s="31" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="J20" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K20" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L20" s="31" t="str"/>
       <x:c r="M20" s="31" t="str">
-        <x:v>保存错误类型、提示和日志编号。</x:v>
+        <x:v>保存错误类型、提示和日志编号。
+执行证据：隔离环境无可用 embedding，未判解析结果。</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="78" customHeight="1">
@@ -2030,15 +2148,22 @@
       <x:c r="G21" s="31" t="str">
         <x:v>只有启用的数据集进入索引队列；停用数据集不被后台任务提前索引；启用后可继续处理。</x:v>
       </x:c>
-      <x:c r="H21" s="32" t="str"/>
+      <x:c r="H21" s="32" t="str">
+        <x:v>停用数据集保持 new/une；启用的数据集进入索引队列并转为 error，证明停用项未入队。因本地 m3e 权重缺失未到 ready。</x:v>
+      </x:c>
       <x:c r="I21" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J21" s="33"/>
-      <x:c r="K21" s="31" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="J21" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K21" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L21" s="31" t="str"/>
       <x:c r="M21" s="31" t="str">
-        <x:v>记录启用标志、状态和队列日志。</x:v>
+        <x:v>记录启用标志、状态和队列日志。
+执行证据：隔离数据库的启用数据集状态及队列错误记录。</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="78" customHeight="1">
@@ -2067,15 +2192,22 @@
       <x:c r="G22" s="31" t="str">
         <x:v>索引状态可追踪；后台处理不阻塞主要界面操作；完成后数据集进入 ready。</x:v>
       </x:c>
-      <x:c r="H22" s="32" t="str"/>
+      <x:c r="H22" s="32" t="str">
+        <x:v>已观察启用数据集从 new 进入处理并因 embedding 不可用失败；未验证完整状态流转到 ready 或索引期间界面响应。</x:v>
+      </x:c>
       <x:c r="I22" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J22" s="33"/>
-      <x:c r="K22" s="31" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="J22" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K22" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L22" s="31" t="str"/>
       <x:c r="M22" s="31" t="str">
-        <x:v>记录状态时间线和页面响应现象，不预设性能数值。</x:v>
+        <x:v>记录状态时间线和页面响应现象，不预设性能数值。
+执行证据：异步队列状态；缺少本地 embedding 权重。</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="78" customHeight="1">
@@ -2104,15 +2236,22 @@
       <x:c r="G23" s="31" t="str">
         <x:v>已索引内容可参与搜索/问答；结果来源指向正确数据集和文件。</x:v>
       </x:c>
-      <x:c r="H23" s="32" t="str"/>
+      <x:c r="H23" s="32" t="str">
+        <x:v>缺少本地 embedding 权重，无法生成 ready 向量并验证搜索/问答召回及来源。</x:v>
+      </x:c>
       <x:c r="I23" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J23" s="33"/>
-      <x:c r="K23" s="31" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="J23" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K23" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L23" s="31" t="str"/>
       <x:c r="M23" s="31" t="str">
-        <x:v>记录查询、命中片段和来源对象 ID。</x:v>
+        <x:v>记录查询、命中片段和来源对象 ID。
+执行证据：向量索引前置条件未满足。</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="78" customHeight="1">
@@ -2142,15 +2281,22 @@
       <x:c r="G24" s="31" t="str">
         <x:v>失败原因可查询；重试后状态可恢复；成功后旧有效错误被标记解决或清理。</x:v>
       </x:c>
-      <x:c r="H24" s="32" t="str"/>
+      <x:c r="H24" s="32" t="str">
+        <x:v>索引失败由缺失 embedding 权重触发；无法修复模型前置条件后重试并验证错误清理。</x:v>
+      </x:c>
       <x:c r="I24" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J24" s="33"/>
-      <x:c r="K24" s="31" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="J24" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K24" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L24" s="31" t="str"/>
       <x:c r="M24" s="31" t="str">
-        <x:v>保留失败和恢复两个阶段的错误编号。</x:v>
+        <x:v>保留失败和恢复两个阶段的错误编号。
+执行证据：索引状态和错误记录；无可用模型资源。</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="78" customHeight="1">
@@ -2179,15 +2325,22 @@
       <x:c r="G25" s="31" t="str">
         <x:v>摘要任务按状态推进；生成内容可查询；来源数据集关联正确；失败时保留原因。</x:v>
       </x:c>
-      <x:c r="H25" s="32" t="str"/>
+      <x:c r="H25" s="32" t="str">
+        <x:v>自动摘要生成需要 ready 向量索引和 LLM 服务；本机未配置 LLM。</x:v>
+      </x:c>
       <x:c r="I25" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J25" s="33"/>
-      <x:c r="K25" s="31" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="J25" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K25" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L25" s="31" t="str"/>
       <x:c r="M25" s="31" t="str">
-        <x:v>记录摘要 ID、状态和模型错误（如有）。</x:v>
+        <x:v>记录摘要 ID、状态和模型错误（如有）。
+执行证据：模型/索引前置条件未满足。</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="78" customHeight="1">
@@ -2217,15 +2370,22 @@
       <x:c r="G26" s="31" t="str">
         <x:v>摘要来源标记为人工；修改后检索使用新内容；删除后关系记录和对应向量均不再返回。</x:v>
       </x:c>
-      <x:c r="H26" s="32" t="str"/>
+      <x:c r="H26" s="32" t="str">
+        <x:v>人工摘要向量新增、修改和删除同步依赖可用向量模型；当前没有可加载 embedding 权重。</x:v>
+      </x:c>
       <x:c r="I26" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J26" s="33"/>
-      <x:c r="K26" s="31" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="J26" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K26" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L26" s="31" t="str"/>
       <x:c r="M26" s="31" t="str">
-        <x:v>记录摘要 ID 和更新/删除后的搜索结果。</x:v>
+        <x:v>记录摘要 ID 和更新/删除后的搜索结果。
+执行证据：模型/向量前置条件未满足。</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="78" customHeight="1">
@@ -2255,15 +2415,22 @@
       <x:c r="G27" s="31" t="str">
         <x:v>自动和人工来源可区分；Q&amp;A 可查询维护；候选问题与检索使用最新有效内容。</x:v>
       </x:c>
-      <x:c r="H27" s="32" t="str"/>
+      <x:c r="H27" s="32" t="str">
+        <x:v>自动 Q&amp;A 生成依赖 LLM，人工维护后的向量同步依赖 embedding；相关服务未配置。</x:v>
+      </x:c>
       <x:c r="I27" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J27" s="33"/>
-      <x:c r="K27" s="31" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="J27" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K27" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L27" s="31" t="str"/>
       <x:c r="M27" s="31" t="str">
-        <x:v>记录 Q&amp;A ID、来源类型和候选列表结果。</x:v>
+        <x:v>记录 Q&amp;A ID、来源类型和候选列表结果。
+执行证据：LLM 与 embedding 前置条件未满足。</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="78" customHeight="1">
@@ -2293,15 +2460,22 @@
       <x:c r="G28" s="31" t="str">
         <x:v>三元组字段完整且按规则去重；修改和删除后关系数据与向量索引一致。</x:v>
       </x:c>
-      <x:c r="H28" s="32" t="str"/>
+      <x:c r="H28" s="32" t="str">
+        <x:v>三元组抽取依赖 LLM；编辑和删除后的向量同步还依赖 embedding，均无法完成。</x:v>
+      </x:c>
       <x:c r="I28" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J28" s="33"/>
-      <x:c r="K28" s="31" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="J28" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K28" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L28" s="31" t="str"/>
       <x:c r="M28" s="31" t="str">
-        <x:v>记录三元组 ID、三字段和检索结果。</x:v>
+        <x:v>记录三元组 ID、三字段和检索结果。
+执行证据：LLM 与 embedding 前置条件未满足。</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="78" customHeight="1">
@@ -2331,15 +2505,22 @@
       <x:c r="G29" s="31" t="str">
         <x:v>每个对话绑定正确知识库；消息和对话可重新读取；切换知识库不串用其他库的资料。</x:v>
       </x:c>
-      <x:c r="H29" s="32" t="str"/>
+      <x:c r="H29" s="32" t="str">
+        <x:v>已验证对话记录可创建；两套 ready 知识库及成功模型问答前置条件不具备。</x:v>
+      </x:c>
       <x:c r="I29" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J29" s="33"/>
-      <x:c r="K29" s="31" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="J29" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K29" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L29" s="31" t="str"/>
       <x:c r="M29" s="31" t="str">
-        <x:v>记录知识库 ID、对话 ID 和消息 ID。</x:v>
+        <x:v>记录知识库 ID、对话 ID 和消息 ID。
+执行证据：隔离数据库无 ready 向量索引和 LLM。</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="78" customHeight="1">
@@ -2368,15 +2549,22 @@
       <x:c r="G30" s="31" t="str">
         <x:v>正常回答流式返回；中断后显示兜底消息或明确错误；最终内容与消息记录一致。</x:v>
       </x:c>
-      <x:c r="H30" s="32" t="str"/>
+      <x:c r="H30" s="32" t="str">
+        <x:v>未配置可控模型，无法验证正常流式响应及生成中断过程。</x:v>
+      </x:c>
       <x:c r="I30" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J30" s="33"/>
-      <x:c r="K30" s="31" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="J30" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K30" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L30" s="31" t="str"/>
       <x:c r="M30" s="31" t="str">
-        <x:v>记录流式事件顺序、消息最终状态和日志编号。</x:v>
+        <x:v>记录流式事件顺序、消息最终状态和日志编号。
+执行证据：没有可用或可控 LLM 服务。</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="78" customHeight="1">
@@ -2405,15 +2593,22 @@
       <x:c r="G31" s="31" t="str">
         <x:v>上下文按知识库设置生效；历史消息不被设置修改追溯性改写；参数变化影响后续请求。</x:v>
       </x:c>
-      <x:c r="H31" s="32" t="str"/>
+      <x:c r="H31" s="32" t="str">
+        <x:v>多轮历史与上下文差异需要可观察的 LLM 调用；当前没有模型服务。</x:v>
+      </x:c>
       <x:c r="I31" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J31" s="33"/>
-      <x:c r="K31" s="31" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="J31" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K31" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L31" s="31" t="str"/>
       <x:c r="M31" s="31" t="str">
-        <x:v>记录配置值和模型可观察到的上下文差异。</x:v>
+        <x:v>记录配置值和模型可观察到的上下文差异。
+执行证据：没有可用 LLM 服务。</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="78" customHeight="1">
@@ -2442,15 +2637,22 @@
       <x:c r="G32" s="31" t="str">
         <x:v>答案引用含计划要求的来源字段；历史消息保留对应引用快照；引用能追溯到稳定来源对象。</x:v>
       </x:c>
-      <x:c r="H32" s="32" t="str"/>
+      <x:c r="H32" s="32" t="str">
+        <x:v>没有可检索向量内容和 LLM 回答，无法验证引用字段及历史引用快照。</x:v>
+      </x:c>
       <x:c r="I32" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J32" s="33"/>
-      <x:c r="K32" s="31" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="J32" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K32" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L32" s="31" t="str"/>
       <x:c r="M32" s="31" t="str">
-        <x:v>保存消息 ID、引用对象 ID 和脱敏截图。</x:v>
+        <x:v>保存消息 ID、引用对象 ID 和脱敏截图。
+执行证据：embedding 与 LLM 前置条件未满足。</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="78" customHeight="1">
@@ -2479,15 +2681,22 @@
       <x:c r="G33" s="31" t="str">
         <x:v>搜索可处理关键词或自然语言；结果相关且受检索设置影响；未索引内容不被错误返回。</x:v>
       </x:c>
-      <x:c r="H33" s="32" t="str"/>
+      <x:c r="H33" s="32" t="str">
+        <x:v>没有可用向量集合，无法比较关键词、语义查询和 TopK/阈值变化。</x:v>
+      </x:c>
       <x:c r="I33" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J33" s="33"/>
-      <x:c r="K33" s="31" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="J33" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K33" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L33" s="31" t="str"/>
       <x:c r="M33" s="31" t="str">
-        <x:v>记录查询文本、TopK、阈值和结果来源。</x:v>
+        <x:v>记录查询文本、TopK、阈值和结果来源。
+执行证据：embedding 前置条件未满足。</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="78" customHeight="1">
@@ -2516,15 +2725,22 @@
       <x:c r="G34" s="31" t="str">
         <x:v>每条结果包含来源信息；跳转目标与结果对象一致；目标不可用时给出明确反馈。</x:v>
       </x:c>
-      <x:c r="H34" s="32" t="str"/>
+      <x:c r="H34" s="32" t="str">
+        <x:v>没有索引搜索结果，无法核验来源卡片及实际页面跳转。</x:v>
+      </x:c>
       <x:c r="I34" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J34" s="33"/>
-      <x:c r="K34" s="31" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="J34" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K34" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L34" s="31" t="str"/>
       <x:c r="M34" s="31" t="str">
-        <x:v>记录来源 ID、跳转目标和页面结果。</x:v>
+        <x:v>记录来源 ID、跳转目标和页面结果。
+执行证据：向量索引和浏览器操作未完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="78" customHeight="1">
@@ -2554,15 +2770,22 @@
       <x:c r="G35" s="31" t="str">
         <x:v>历史可保存和删除；无结果查询不会显示伪造内容或错误来源；页面提示明确。</x:v>
       </x:c>
-      <x:c r="H35" s="32" t="str"/>
+      <x:c r="H35" s="32" t="str">
+        <x:v>搜索请求写入历史后因向量模型缺失返回 HTTP 500；历史删除不能替代完整的搜索结果和无结果 UI 验证。</x:v>
+      </x:c>
       <x:c r="I35" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J35" s="33"/>
-      <x:c r="K35" s="31" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="J35" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K35" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L35" s="31" t="str"/>
       <x:c r="M35" s="31" t="str">
-        <x:v>记录历史 ID、结果条数和无结果页面截图。</x:v>
+        <x:v>记录历史 ID、结果条数和无结果页面截图。
+执行证据：隔离搜索 API；模型异常响应和历史记录清理。</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="78" customHeight="1">
@@ -2591,15 +2814,22 @@
       <x:c r="G36" s="31" t="str">
         <x:v>只有满足索引和启用规则的数据集参与检索；状态改变后搜索范围按规则更新。</x:v>
       </x:c>
-      <x:c r="H36" s="32" t="str"/>
+      <x:c r="H36" s="32" t="str">
+        <x:v>没有可用向量索引，无法比较 ready、未索引、停用数据集的真实搜索命中范围。</x:v>
+      </x:c>
       <x:c r="I36" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J36" s="33"/>
-      <x:c r="K36" s="31" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="J36" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K36" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L36" s="31" t="str"/>
       <x:c r="M36" s="31" t="str">
-        <x:v>记录每个短句的命中情况和数据集状态。</x:v>
+        <x:v>记录每个短句的命中情况和数据集状态。
+执行证据：embedding 前置条件未满足。</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="78" customHeight="1">
@@ -2628,15 +2858,22 @@
       <x:c r="G37" s="31" t="str">
         <x:v>文档集、文档可创建和编辑；修改结果持久化；列表和详情保持一致。</x:v>
       </x:c>
-      <x:c r="H37" s="32" t="str"/>
+      <x:c r="H37" s="32" t="str">
+        <x:v>文档集和文档 API 创建成功；文档标题和正文修改后可重新读取。</x:v>
+      </x:c>
       <x:c r="I37" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J37" s="33"/>
-      <x:c r="K37" s="31" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="J37" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K37" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L37" s="31" t="str"/>
       <x:c r="M37" s="31" t="str">
-        <x:v>记录文档集 ID 和文档 ID。</x:v>
+        <x:v>记录文档集 ID 和文档 ID。
+执行证据：隔离文档集/文档 API。</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="78" customHeight="1">
@@ -2665,15 +2902,22 @@
       <x:c r="G38" s="31" t="str">
         <x:v>内容修改生成可追溯版本快照；版本顺序明确；旧版本内容未被覆盖。</x:v>
       </x:c>
-      <x:c r="H38" s="32" t="str"/>
+      <x:c r="H38" s="32" t="str">
+        <x:v>修改正文后生成版本快照；直接核验隔离数据库中的版本行和正文。当前没有版本列表 API。</x:v>
+      </x:c>
       <x:c r="I38" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J38" s="33"/>
-      <x:c r="K38" s="31" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="J38" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K38" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L38" s="31" t="str"/>
       <x:c r="M38" s="31" t="str">
-        <x:v>记录文档 ID、版本号和修改前后内容摘要。</x:v>
+        <x:v>记录文档 ID、版本号和修改前后内容摘要。
+执行证据：隔离 SQLite 文档及版本行。</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="78" customHeight="1">
@@ -2702,15 +2946,22 @@
       <x:c r="G39" s="31" t="str">
         <x:v>转入前校验知识库存在性和权限；数据集关联正确文档版本；索引 ready 后可检索。</x:v>
       </x:c>
-      <x:c r="H39" s="32" t="str"/>
+      <x:c r="H39" s="32" t="str">
+        <x:v>文档已生成关联数据集和 docVerId；索引、ready 状态和搜索命中因 embedding 不可用未验证。</x:v>
+      </x:c>
       <x:c r="I39" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J39" s="33"/>
-      <x:c r="K39" s="31" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="J39" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K39" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L39" s="31" t="str"/>
       <x:c r="M39" s="31" t="str">
-        <x:v>记录文档、版本、数据集 ID 和检索来源。</x:v>
+        <x:v>记录文档、版本、数据集 ID 和检索来源。
+执行证据：隔离文档转数据集 API；索引前置条件未满足。</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="78" customHeight="1">
@@ -2739,15 +2990,22 @@
       <x:c r="G40" s="31" t="str">
         <x:v>删除文档/文档集时关联版本按规则清理；其他文档集和文档不受影响。</x:v>
       </x:c>
-      <x:c r="H40" s="32" t="str"/>
+      <x:c r="H40" s="32" t="str">
+        <x:v>删除文档集后其文档及版本均删除；另一个文档集中的无关文档保留。</x:v>
+      </x:c>
       <x:c r="I40" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J40" s="33"/>
-      <x:c r="K40" s="31" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="J40" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K40" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L40" s="31" t="str"/>
       <x:c r="M40" s="31" t="str">
-        <x:v>保存删除前后对象清单。</x:v>
+        <x:v>保存删除前后对象清单。
+执行证据：隔离 SQLite 删除前后对象计数。</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="78" customHeight="1">
@@ -2777,15 +3035,22 @@
       <x:c r="G41" s="31" t="str">
         <x:v>数据集删除后其分段、摘要、自动 Q&amp;A、三元组、错误记录、文件和向量无残留；其他数据集不受影响。</x:v>
       </x:c>
-      <x:c r="H41" s="32" t="str"/>
+      <x:c r="H41" s="32" t="str">
+        <x:v>独立数据集删除已移除关系记录和上传文件；本次没有派生向量和增强对象，无法证明完整关联清理。</x:v>
+      </x:c>
       <x:c r="I41" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J41" s="33"/>
-      <x:c r="K41" s="31" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="J41" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K41" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L41" s="31" t="str"/>
       <x:c r="M41" s="31" t="str">
-        <x:v>仅使用备份可恢复数据；保存删除前后对象清单。</x:v>
+        <x:v>仅使用备份可恢复数据；保存删除前后对象清单。
+执行证据：隔离数据集删除 API；没有向量对象。</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="78" customHeight="1">
@@ -2815,15 +3080,24 @@
       <x:c r="G42" s="31" t="str">
         <x:v>被删知识库的关联对象按设计清理且无脏引用或向量；其他知识库数据保持完整。</x:v>
       </x:c>
-      <x:c r="H42" s="32" t="str"/>
+      <x:c r="H42" s="32" t="str">
+        <x:v>删除知识库后数据集、对话、消息和搜索历史记录均已清理，但已上传文件仍留在磁盘，见 DEF-WKB-004。</x:v>
+      </x:c>
       <x:c r="I42" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J42" s="33"/>
-      <x:c r="K42" s="31" t="str"/>
-      <x:c r="L42" s="31" t="str"/>
+        <x:v>失败</x:v>
+      </x:c>
+      <x:c r="J42" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K42" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
+      <x:c r="L42" s="31" t="str">
+        <x:v>DEF-WKB-004</x:v>
+      </x:c>
       <x:c r="M42" s="31" t="str">
-        <x:v>仅在可恢复测试数据上执行，保存删除前后清单。</x:v>
+        <x:v>仅在可恢复测试数据上执行，保存删除前后清单。
+执行证据：隔离 SQLite 关联记录及本地文件删除前后检查。</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="78" customHeight="1">
@@ -2852,15 +3126,22 @@
       <x:c r="G43" s="31" t="str">
         <x:v>目录删除不删除数据集；数据集目录标识清空并回到未分类；索引内容不受影响。</x:v>
       </x:c>
-      <x:c r="H43" s="32" t="str"/>
+      <x:c r="H43" s="32" t="str">
+        <x:v>删除目录后数据集仍存在，ctlgId 清空并回到未分类。</x:v>
+      </x:c>
       <x:c r="I43" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J43" s="33"/>
-      <x:c r="K43" s="31" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="J43" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K43" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L43" s="31" t="str"/>
       <x:c r="M43" s="31" t="str">
-        <x:v>记录目录 ID、数据集 ID 和目录字段前后值。</x:v>
+        <x:v>记录目录 ID、数据集 ID 和目录字段前后值。
+执行证据：隔离目录及数据集 API 回读。</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="78" customHeight="1">
@@ -2889,15 +3170,22 @@
       <x:c r="G44" s="31" t="str">
         <x:v>修改后对应向量更新；删除后向量移除；其他分段仍可检索。</x:v>
       </x:c>
-      <x:c r="H44" s="32" t="str"/>
+      <x:c r="H44" s="32" t="str">
+        <x:v>没有向量索引，无法验证分段修改和删除后的向量同步。</x:v>
+      </x:c>
       <x:c r="I44" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J44" s="33"/>
-      <x:c r="K44" s="31" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="J44" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K44" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L44" s="31" t="str"/>
       <x:c r="M44" s="31" t="str">
-        <x:v>记录分段 ID、新旧搜索结果和向量对象状态。</x:v>
+        <x:v>记录分段 ID、新旧搜索结果和向量对象状态。
+执行证据：embedding 前置条件未满足。</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="78" customHeight="1">
@@ -2926,15 +3214,24 @@
       <x:c r="G45" s="31" t="str">
         <x:v>私有知识库只对所属用户可见；列表和直接访问保持一致，不泄露名称或内容。</x:v>
       </x:c>
-      <x:c r="H45" s="32" t="str"/>
+      <x:c r="H45" s="32" t="str">
+        <x:v>不同 token 字符串仍可读取私有知识库；中间件将请求统一映射到 client_default_user，权限隔离失效，见 DEF-WKB-001。</x:v>
+      </x:c>
       <x:c r="I45" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J45" s="33"/>
-      <x:c r="K45" s="31" t="str"/>
-      <x:c r="L45" s="31" t="str"/>
+        <x:v>失败</x:v>
+      </x:c>
+      <x:c r="J45" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K45" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
+      <x:c r="L45" s="31" t="str">
+        <x:v>DEF-WKB-001</x:v>
+      </x:c>
       <x:c r="M45" s="31" t="str">
-        <x:v>记录用户标识、列表结果和访问响应。</x:v>
+        <x:v>记录用户标识、列表结果和访问响应。
+执行证据：两个合成 token 的隔离知识库列表/详情请求。</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="78" customHeight="1">
@@ -2963,15 +3260,24 @@
       <x:c r="G46" s="31" t="str">
         <x:v>公开知识库按设计对其他用户可见；读取与修改权限分别遵循规则；私有对象仍不可见。</x:v>
       </x:c>
-      <x:c r="H46" s="32" t="str"/>
+      <x:c r="H46" s="32" t="str">
+        <x:v>另一 token 可读取公开知识库且 optAuth 返回 alter，并可修改对象；未实现只读访问范围，见 DEF-WKB-001。</x:v>
+      </x:c>
       <x:c r="I46" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J46" s="33"/>
-      <x:c r="K46" s="31" t="str"/>
-      <x:c r="L46" s="31" t="str"/>
+        <x:v>失败</x:v>
+      </x:c>
+      <x:c r="J46" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K46" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
+      <x:c r="L46" s="31" t="str">
+        <x:v>DEF-WKB-001</x:v>
+      </x:c>
       <x:c r="M46" s="31" t="str">
-        <x:v>记录可见对象 ID 和读写权限结果。</x:v>
+        <x:v>记录可见对象 ID 和读写权限结果。
+执行证据：公开知识库详情与编辑 API。</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="78" customHeight="1">
@@ -3000,15 +3306,24 @@
       <x:c r="G47" s="31" t="str">
         <x:v>写操作返回明确业务错误；数据库和向量数据未被修改；错误响应不泄露敏感内容。</x:v>
       </x:c>
-      <x:c r="H47" s="32" t="str"/>
+      <x:c r="H47" s="32" t="str">
+        <x:v>使用另一 token 修改私有知识库名称成功，未被拒绝，见 DEF-WKB-001。</x:v>
+      </x:c>
       <x:c r="I47" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J47" s="33"/>
-      <x:c r="K47" s="31" t="str"/>
-      <x:c r="L47" s="31" t="str"/>
+        <x:v>失败</x:v>
+      </x:c>
+      <x:c r="J47" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K47" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
+      <x:c r="L47" s="31" t="str">
+        <x:v>DEF-WKB-001</x:v>
+      </x:c>
       <x:c r="M47" s="31" t="str">
-        <x:v>记录请求对象 ID、错误码和所有者复查结果。</x:v>
+        <x:v>记录请求对象 ID、错误码和所有者复查结果。
+执行证据：两个合成 token 的隔离知识库编辑 API。</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="78" customHeight="1">
@@ -3037,15 +3352,24 @@
       <x:c r="G48" s="31" t="str">
         <x:v>未授权对象不可读取；关联消息、引用和搜索记录不泄露；失败原因可追踪。</x:v>
       </x:c>
-      <x:c r="H48" s="32" t="str"/>
+      <x:c r="H48" s="32" t="str">
+        <x:v>使用另一 token 可按对象 ID 直接读取私有知识库，未被拒绝，见 DEF-WKB-001。</x:v>
+      </x:c>
       <x:c r="I48" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J48" s="33"/>
-      <x:c r="K48" s="31" t="str"/>
-      <x:c r="L48" s="31" t="str"/>
+        <x:v>失败</x:v>
+      </x:c>
+      <x:c r="J48" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K48" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
+      <x:c r="L48" s="31" t="str">
+        <x:v>DEF-WKB-001</x:v>
+      </x:c>
       <x:c r="M48" s="31" t="str">
-        <x:v>保存接口响应摘要，避免记录私有正文。</x:v>
+        <x:v>保存接口响应摘要，避免记录私有正文。
+执行证据：两个合成 token 的隔离详情 API。</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="78" customHeight="1">
@@ -3075,15 +3399,22 @@
       <x:c r="G49" s="31" t="str">
         <x:v>核心闭环各步骤完成；引用来源正确；删除后无残留；本轮变更未引入主链路回退。</x:v>
       </x:c>
-      <x:c r="H49" s="32" t="str"/>
+      <x:c r="H49" s="32" t="str">
+        <x:v>没有可用模型和向量索引，无法完成导入、索引、增强、问答、搜索、引用和删除的端到端闭环。</x:v>
+      </x:c>
       <x:c r="I49" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J49" s="33"/>
-      <x:c r="K49" s="31" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="J49" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K49" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L49" s="31" t="str"/>
       <x:c r="M49" s="31" t="str">
-        <x:v>记录版本、每步对象 ID 和失败/回归项。</x:v>
+        <x:v>记录版本、每步对象 ID 和失败/回归项。
+执行证据：LLM 与 embedding 前置条件未满足。</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="78" customHeight="1">
@@ -3112,15 +3443,22 @@
       <x:c r="G50" s="31" t="str">
         <x:v>关系数据与向量数据在操作完成后保持一致；异常可定位并可按维护流程重建。</x:v>
       </x:c>
-      <x:c r="H50" s="32" t="str"/>
+      <x:c r="H50" s="32" t="str">
+        <x:v>关系记录可局部核验；没有向量集合，无法证明关系库、文件与向量库全链路一致。</x:v>
+      </x:c>
       <x:c r="I50" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J50" s="33"/>
-      <x:c r="K50" s="31" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="J50" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K50" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L50" s="31" t="str"/>
       <x:c r="M50" s="31" t="str">
-        <x:v>保存对象 ID、查询结果和一致性检查记录。</x:v>
+        <x:v>保存对象 ID、查询结果和一致性检查记录。
+执行证据：embedding 前置条件未满足。</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="78" customHeight="1">
@@ -3149,15 +3487,22 @@
       <x:c r="G51" s="31" t="str">
         <x:v>两种入口的主要功能可用；内容不被裁切；中文路径可访问；不出现明显横向溢出或未处理错误。</x:v>
       </x:c>
-      <x:c r="H51" s="32" t="str"/>
+      <x:c r="H51" s="32" t="str">
+        <x:v>HTTP/Vite 代理已验证；真实浏览器页面、Tauri 桌面端、窗口适配及截图留待人工检查。</x:v>
+      </x:c>
       <x:c r="I51" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J51" s="33"/>
-      <x:c r="K51" s="31" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="J51" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K51" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L51" s="31" t="str"/>
       <x:c r="M51" s="31" t="str">
-        <x:v>记录系统/浏览器版本、窗口尺寸和截图。</x:v>
+        <x:v>记录系统/浏览器版本、窗口尺寸和截图。
+执行证据：运行证据 S01-S06 待人工完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="78" customHeight="1">
@@ -3186,15 +3531,22 @@
       <x:c r="G52" s="31" t="str">
         <x:v>文档范围、术语和状态规则一致；工作簿覆盖测试计划 TP-001 至 TP-012；未执行用例不显示为通过。</x:v>
       </x:c>
-      <x:c r="H52" s="32" t="str"/>
+      <x:c r="H52" s="32" t="str">
+        <x:v>静态文档回归和工作簿覆盖检查通过；TP-001 至 TP-012 各 4 条，共 48 条。产品功能结论以本表逐条结果为准。</x:v>
+      </x:c>
       <x:c r="I52" s="35" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="J52" s="33"/>
-      <x:c r="K52" s="31" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="J52" s="33" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K52" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="L52" s="31" t="str"/>
       <x:c r="M52" s="31" t="str">
-        <x:v>记录发现的文档差异、责任文档和修订建议。</x:v>
+        <x:v>记录发现的文档差异、责任文档和修订建议。
+执行证据：Python 全量文档/成绩书测试及工作簿覆盖核验。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3215,7 +3567,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e3968e754514196"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2864e0a640934ce7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3491,7 +3843,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbee11af59bef44bc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20606707296a4543"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3658,7 +4010,7 @@
       </x:c>
       <x:c r="B11" s="43" t="n">
         <x:f>COUNTIFS('测试项目'!I5:I52,"通过")</x:f>
-        <x:v>0</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C11" s="2"/>
       <x:c r="D11" s="2"/>
@@ -3674,7 +4026,7 @@
       </x:c>
       <x:c r="B12" s="43" t="n">
         <x:f>COUNTIFS('测试项目'!I5:I52,"失败")</x:f>
-        <x:v>0</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C12" s="2"/>
       <x:c r="D12" s="2"/>
@@ -3690,7 +4042,7 @@
       </x:c>
       <x:c r="B13" s="43" t="n">
         <x:f>COUNTIFS('测试项目'!I5:I52,"阻塞")</x:f>
-        <x:v>0</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C13" s="2"/>
       <x:c r="D13" s="2"/>
@@ -3706,7 +4058,7 @@
       </x:c>
       <x:c r="B14" s="43" t="n">
         <x:f>COUNTIFS('测试项目'!I5:I52,"未执行")</x:f>
-        <x:v>48</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C14" s="2"/>
       <x:c r="D14" s="2"/>
@@ -3738,7 +4090,7 @@
       </x:c>
       <x:c r="B16" s="43" t="n">
         <x:f>B11+B12</x:f>
-        <x:v>0</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C16" s="2"/>
       <x:c r="D16" s="2"/>
@@ -3752,9 +4104,9 @@
       <x:c r="A17" s="40" t="str">
         <x:v>通过率</x:v>
       </x:c>
-      <x:c r="B17" s="44" t="str">
+      <x:c r="B17" s="44" t="n">
         <x:f>IF(B16=0,"待执行",B11/B16)</x:f>
-        <x:v>待执行</x:v>
+        <x:v>0.6363636363636364</x:v>
       </x:c>
       <x:c r="C17" s="2"/>
       <x:c r="D17" s="2"/>
@@ -3786,7 +4138,7 @@
       </x:c>
       <x:c r="B19" s="49" t="str">
         <x:f>IF(B12&gt;0,"不通过：存在失败用例",IF(B13&gt;0,"阻塞：需处理阻塞用例",IF(B18&gt;0,"未完成：存在未填结论",IF(B14&gt;0,"未完成：请先执行全部用例",IF(B15&gt;0,"未完成：存在不适用项待确认","通过")))))</x:f>
-        <x:v>未完成：请先执行全部用例</x:v>
+        <x:v>不通过：存在失败用例</x:v>
       </x:c>
       <x:c r="C19" s="2"/>
       <x:c r="D19" s="2"/>
@@ -3942,58 +4294,118 @@
       <x:c r="H29" s="2"/>
       <x:c r="I29" s="2"/>
     </x:row>
-    <x:row r="30" ht="25" customHeight="1">
-      <x:c r="A30" s="31" t="str"/>
-      <x:c r="B30" s="31" t="str"/>
-      <x:c r="C30" s="31" t="str"/>
-      <x:c r="D30" s="31" t="str"/>
-      <x:c r="E30" s="31" t="str"/>
-      <x:c r="F30" s="31" t="str"/>
-      <x:c r="G30" s="53"/>
+    <x:row r="30" ht="54" customHeight="1">
+      <x:c r="A30" s="31" t="str">
+        <x:v>DEF-WKB-001</x:v>
+      </x:c>
+      <x:c r="B30" s="31" t="str">
+        <x:v>TC-WKB-041~044</x:v>
+      </x:c>
+      <x:c r="C30" s="31" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="D30" s="31" t="str">
+        <x:v>请求中间件把不同 token 映射为同一 client_default_user；私有知识库可被其他 token 读取和修改，公开库也返回 alter。</x:v>
+      </x:c>
+      <x:c r="E30" s="31" t="str">
+        <x:v>待修复；阻断多用户权限验收。</x:v>
+      </x:c>
+      <x:c r="F30" s="31" t="str">
+        <x:v>待分配</x:v>
+      </x:c>
+      <x:c r="G30" s="53" t="str"/>
       <x:c r="H30" s="2"/>
       <x:c r="I30" s="2"/>
     </x:row>
-    <x:row r="31" ht="25" customHeight="1">
-      <x:c r="A31" s="31" t="str"/>
-      <x:c r="B31" s="31" t="str"/>
-      <x:c r="C31" s="31" t="str"/>
-      <x:c r="D31" s="31" t="str"/>
-      <x:c r="E31" s="31" t="str"/>
-      <x:c r="F31" s="31" t="str"/>
-      <x:c r="G31" s="53"/>
+    <x:row r="31" ht="54" customHeight="1">
+      <x:c r="A31" s="31" t="str">
+        <x:v>DEF-WKB-002</x:v>
+      </x:c>
+      <x:c r="B31" s="31" t="str">
+        <x:v>TC-WKB-010</x:v>
+      </x:c>
+      <x:c r="C31" s="31" t="str">
+        <x:v>中</x:v>
+      </x:c>
+      <x:c r="D31" s="31" t="str">
+        <x:v>知识库名称为空时，创建接口仍返回成功并保存空名称记录。</x:v>
+      </x:c>
+      <x:c r="E31" s="31" t="str">
+        <x:v>待修复；增加名称校验并回归创建接口。</x:v>
+      </x:c>
+      <x:c r="F31" s="31" t="str">
+        <x:v>待分配</x:v>
+      </x:c>
+      <x:c r="G31" s="53" t="str"/>
       <x:c r="H31" s="2"/>
       <x:c r="I31" s="2"/>
     </x:row>
-    <x:row r="32" ht="25" customHeight="1">
-      <x:c r="A32" s="31" t="str"/>
-      <x:c r="B32" s="31" t="str"/>
-      <x:c r="C32" s="31" t="str"/>
-      <x:c r="D32" s="31" t="str"/>
-      <x:c r="E32" s="31" t="str"/>
-      <x:c r="F32" s="31" t="str"/>
-      <x:c r="G32" s="53"/>
+    <x:row r="32" ht="54" customHeight="1">
+      <x:c r="A32" s="31" t="str">
+        <x:v>DEF-WKB-003</x:v>
+      </x:c>
+      <x:c r="B32" s="31" t="str">
+        <x:v>TC-WKB-015</x:v>
+      </x:c>
+      <x:c r="C32" s="31" t="str">
+        <x:v>中</x:v>
+      </x:c>
+      <x:c r="D32" s="31" t="str">
+        <x:v>链接导入接口接受 not-a-valid-url 并保存为数据集，未校验 URL 格式。</x:v>
+      </x:c>
+      <x:c r="E32" s="31" t="str">
+        <x:v>待修复；增加格式校验并覆盖无效输入。</x:v>
+      </x:c>
+      <x:c r="F32" s="31" t="str">
+        <x:v>待分配</x:v>
+      </x:c>
+      <x:c r="G32" s="53" t="str"/>
       <x:c r="H32" s="2"/>
       <x:c r="I32" s="2"/>
     </x:row>
-    <x:row r="33" ht="25" customHeight="1">
-      <x:c r="A33" s="31" t="str"/>
-      <x:c r="B33" s="31" t="str"/>
-      <x:c r="C33" s="31" t="str"/>
-      <x:c r="D33" s="31" t="str"/>
-      <x:c r="E33" s="31" t="str"/>
-      <x:c r="F33" s="31" t="str"/>
-      <x:c r="G33" s="53"/>
+    <x:row r="33" ht="54" customHeight="1">
+      <x:c r="A33" s="31" t="str">
+        <x:v>DEF-WKB-004</x:v>
+      </x:c>
+      <x:c r="B33" s="31" t="str">
+        <x:v>TC-WKB-038</x:v>
+      </x:c>
+      <x:c r="C33" s="31" t="str">
+        <x:v>中</x:v>
+      </x:c>
+      <x:c r="D33" s="31" t="str">
+        <x:v>删除知识库会清除数据库关联记录，但不会删除其本地上传文件。</x:v>
+      </x:c>
+      <x:c r="E33" s="31" t="str">
+        <x:v>待修复；删除后核验本地文件及向量数据清理。</x:v>
+      </x:c>
+      <x:c r="F33" s="31" t="str">
+        <x:v>待分配</x:v>
+      </x:c>
+      <x:c r="G33" s="53" t="str"/>
       <x:c r="H33" s="2"/>
       <x:c r="I33" s="2"/>
     </x:row>
-    <x:row r="34" ht="25" customHeight="1">
-      <x:c r="A34" s="31" t="str"/>
-      <x:c r="B34" s="31" t="str"/>
-      <x:c r="C34" s="31" t="str"/>
-      <x:c r="D34" s="31" t="str"/>
-      <x:c r="E34" s="31" t="str"/>
-      <x:c r="F34" s="31" t="str"/>
-      <x:c r="G34" s="53"/>
+    <x:row r="34" ht="54" customHeight="1">
+      <x:c r="A34" s="31" t="str">
+        <x:v>DEF-WKB-005</x:v>
+      </x:c>
+      <x:c r="B34" s="31" t="str">
+        <x:v>TC-WKB-008</x:v>
+      </x:c>
+      <x:c r="C34" s="31" t="str">
+        <x:v>中</x:v>
+      </x:c>
+      <x:c r="D34" s="31" t="str">
+        <x:v>LLM 客户端初始化失败时 SSE 发出兜底文本，但助手兜底消息未写入对话历史。</x:v>
+      </x:c>
+      <x:c r="E34" s="31" t="str">
+        <x:v>待修复；失败回退后持久化最终消息并补充回归。</x:v>
+      </x:c>
+      <x:c r="F34" s="31" t="str">
+        <x:v>待分配</x:v>
+      </x:c>
+      <x:c r="G34" s="53" t="str"/>
       <x:c r="H34" s="2"/>
       <x:c r="I34" s="2"/>
     </x:row>
@@ -4010,7 +4422,7 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="25" t="str">
-        <x:v>项目实际运行情况（待人工执行）</x:v>
+        <x:v>项目实际运行情况（截图待补充）</x:v>
       </x:c>
       <x:c r="B36" s="25"/>
       <x:c r="C36" s="25"/>
@@ -4023,7 +4435,7 @@
     </x:row>
     <x:row r="37" ht="34" customHeight="1">
       <x:c r="A37" s="54" t="str">
-        <x:v>依据 docs/test_scorebook_manual_run.md 在隔离副本中手动运行并粘贴截图。本区仅记录运行冒烟证据，不替代 48 条用例执行，也不改变交付判定。</x:v>
+        <x:v>隔离副本 API/Vite 冒烟与核心用例已自动执行。S01 至 S06 需补贴真实运行截图；截图待办不替代用例结果，也不改变交付判定。</x:v>
       </x:c>
       <x:c r="B37" s="54"/>
       <x:c r="C37" s="54"/>
@@ -4062,35 +4474,47 @@
       <x:c r="A40" s="59" t="str">
         <x:v>项目版本</x:v>
       </x:c>
-      <x:c r="B40" s="41" t="str"/>
+      <x:c r="B40" s="41" t="str">
+        <x:v>前端 0.1.9；后端基线 3951cd35be53</x:v>
+      </x:c>
       <x:c r="C40" s="41" t="str"/>
       <x:c r="D40" s="41" t="str"/>
       <x:c r="E40" s="59" t="str">
         <x:v>Git 提交</x:v>
       </x:c>
-      <x:c r="F40" s="41" t="str"/>
+      <x:c r="F40" s="41" t="str">
+        <x:v>3951cd35be531084e7ebf2f40444d77bc6dff30c</x:v>
+      </x:c>
       <x:c r="G40" s="41" t="str"/>
       <x:c r="H40" s="59" t="str">
         <x:v>执行人</x:v>
       </x:c>
-      <x:c r="I40" s="41" t="str"/>
+      <x:c r="I40" s="41" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="28" customHeight="1">
       <x:c r="A41" s="59" t="str">
         <x:v>操作系统</x:v>
       </x:c>
-      <x:c r="B41" s="41" t="str"/>
+      <x:c r="B41" s="41" t="str">
+        <x:v>Windows 11 专业版</x:v>
+      </x:c>
       <x:c r="C41" s="41" t="str"/>
       <x:c r="D41" s="41" t="str"/>
       <x:c r="E41" s="59" t="str">
         <x:v>浏览器</x:v>
       </x:c>
-      <x:c r="F41" s="41" t="str"/>
+      <x:c r="F41" s="41" t="str">
+        <x:v>HTTP/Vite 与页面导航已验；截图待贴</x:v>
+      </x:c>
       <x:c r="G41" s="41" t="str"/>
       <x:c r="H41" s="59" t="str">
         <x:v>执行日期</x:v>
       </x:c>
-      <x:c r="I41" s="60"/>
+      <x:c r="I41" s="60" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="28" customHeight="1">
       <x:c r="A42" s="59" t="str">
@@ -4177,12 +4601,16 @@
       </x:c>
       <x:c r="E46" s="31"/>
       <x:c r="F46" s="35" t="str">
-        <x:v>待人工执行</x:v>
-      </x:c>
-      <x:c r="G46" s="53"/>
-      <x:c r="H46" s="31" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="G46" s="53" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H46" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="I46" s="31" t="str">
-        <x:v>S01-health.png</x:v>
+        <x:v>待贴：S01-health.png</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="48" customHeight="1">
@@ -4198,12 +4626,16 @@
       </x:c>
       <x:c r="E47" s="31"/>
       <x:c r="F47" s="35" t="str">
-        <x:v>待人工执行</x:v>
-      </x:c>
-      <x:c r="G47" s="53"/>
-      <x:c r="H47" s="31" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="G47" s="53" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H47" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="I47" s="31" t="str">
-        <x:v>S02-workspace.png</x:v>
+        <x:v>待贴：S02-workspace.png</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="48" customHeight="1">
@@ -4219,12 +4651,16 @@
       </x:c>
       <x:c r="E48" s="31"/>
       <x:c r="F48" s="35" t="str">
-        <x:v>待人工执行</x:v>
-      </x:c>
-      <x:c r="G48" s="53"/>
-      <x:c r="H48" s="31" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="G48" s="53" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H48" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="I48" s="31" t="str">
-        <x:v>S03-model-settings.png</x:v>
+        <x:v>待贴：S03-model-settings.png</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="48" customHeight="1">
@@ -4240,12 +4676,16 @@
       </x:c>
       <x:c r="E49" s="31"/>
       <x:c r="F49" s="35" t="str">
-        <x:v>待人工执行</x:v>
-      </x:c>
-      <x:c r="G49" s="53"/>
-      <x:c r="H49" s="31" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="G49" s="53" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H49" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="I49" s="31" t="str">
-        <x:v>S04-repository.png</x:v>
+        <x:v>待贴：S04-repository.png</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="48" customHeight="1">
@@ -4261,12 +4701,16 @@
       </x:c>
       <x:c r="E50" s="31"/>
       <x:c r="F50" s="35" t="str">
-        <x:v>待人工执行</x:v>
-      </x:c>
-      <x:c r="G50" s="53"/>
-      <x:c r="H50" s="31" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="G50" s="53" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H50" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="I50" s="31" t="str">
-        <x:v>S05-dataset.png</x:v>
+        <x:v>待贴：S05-dataset.png</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="48" customHeight="1">
@@ -4282,12 +4726,16 @@
       </x:c>
       <x:c r="E51" s="31"/>
       <x:c r="F51" s="35" t="str">
-        <x:v>待人工执行</x:v>
-      </x:c>
-      <x:c r="G51" s="53"/>
-      <x:c r="H51" s="31" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="G51" s="53" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H51" s="31" t="str">
+        <x:v>自动化执行</x:v>
+      </x:c>
       <x:c r="I51" s="31" t="str">
-        <x:v>S06-search-chat.png</x:v>
+        <x:v>待贴：S06-search-chat.png</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -5014,7 +5462,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R132dae3e76ab429c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree61bff0f2e94137"/>
   </x:tableParts>
 </x:worksheet>
 </file>